--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -2915,7 +2915,7 @@
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
@@ -4481,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>16</v>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA9" s="4" t="n">
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>20</v>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA10" s="4" t="n">
@@ -4976,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>16</v>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="Z12" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA12" s="4" t="n">
@@ -5139,7 +5139,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>16</v>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Z13" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA13" s="4" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -5310,10 +5310,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>1</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA14" s="4" t="n">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -5487,10 +5487,10 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>1</v>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA15" s="4" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -5664,10 +5664,10 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M16" s="4" t="n">
         <v>1</v>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="Z16" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA16" s="4" t="n">
@@ -5841,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>16</v>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="Z17" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA17" s="4" t="n">
@@ -6018,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>20</v>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="Z18" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA18" s="4" t="n">
@@ -6195,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>20</v>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="Z19" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA19" s="4" t="n">
@@ -7024,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>16</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA24" s="4" t="n">
@@ -7201,7 +7201,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>16</v>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="Z25" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA25" s="4" t="n">
@@ -7740,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="L28" s="4" t="n">
         <v>20</v>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="Z28" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA28" s="4" t="n">
@@ -7945,7 +7945,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>16</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="Z29" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA29" s="4" t="n">
@@ -8144,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>16</v>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="Z30" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA30" s="4" t="n">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -8693,10 +8693,10 @@
         <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>1</v>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="Z33" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA33" s="4" t="n">
@@ -8876,7 +8876,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>16</v>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="Z34" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA34" s="4" t="n">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -9061,10 +9061,10 @@
         <v>1</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>1</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="Z35" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA35" s="4" t="n">
@@ -9244,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>20</v>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="Z36" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA36" s="4" t="n">
@@ -10096,14 +10096,14 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>防禦型</t>
+          <t>力量型</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>560</v>
+        <v>380</v>
       </c>
       <c r="L41" s="4" t="n">
         <v>16</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="Z41" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA41" s="4" t="n">
@@ -10160,10 +10160,10 @@
       </c>
       <c r="AC41" s="4" t="inlineStr"/>
       <c r="AD41" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE41" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF41" s="4" t="n">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>16</v>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="Z42" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA42" s="4" t="n">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -10471,10 +10471,10 @@
         <v>1</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>1</v>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="Z43" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA43" s="4" t="n">
@@ -10654,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L44" s="4" t="n">
         <v>16</v>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="Z44" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA44" s="4" t="n">
@@ -10830,14 +10830,14 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>防禦型</t>
+          <t>力量型</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="L45" s="4" t="n">
         <v>12</v>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="Z45" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 16]</t>
         </is>
       </c>
       <c r="AA45" s="4" t="n">
@@ -10894,10 +10894,10 @@
       </c>
       <c r="AC45" s="4" t="inlineStr"/>
       <c r="AD45" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE45" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF45" s="4" t="n">
         <v>1</v>
@@ -11017,14 +11017,14 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>防禦型</t>
+          <t>力量型</t>
         </is>
       </c>
       <c r="J46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>560</v>
+        <v>380</v>
       </c>
       <c r="L46" s="4" t="n">
         <v>16</v>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="Z46" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA46" s="4" t="n">
@@ -11081,10 +11081,10 @@
       </c>
       <c r="AC46" s="4" t="inlineStr"/>
       <c r="AD46" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE46" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF46" s="4" t="n">
         <v>1</v>
@@ -11204,14 +11204,14 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>防禦型</t>
+          <t>力量型</t>
         </is>
       </c>
       <c r="J47" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="L47" s="4" t="n">
         <v>8</v>
@@ -11268,10 +11268,10 @@
       </c>
       <c r="AC47" s="4" t="inlineStr"/>
       <c r="AD47" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE47" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF47" s="4" t="n">
         <v>1</v>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -11390,10 +11390,10 @@
         <v>1</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M48" s="4" t="n">
         <v>1</v>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="Z48" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA48" s="4" t="n">
@@ -11575,7 +11575,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L49" s="4" t="n">
         <v>16</v>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="Z49" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA49" s="4" t="n">
@@ -11760,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L50" s="4" t="n">
         <v>16</v>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="Z50" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA50" s="4" t="n">
@@ -11943,7 +11943,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="L51" s="4" t="n">
         <v>16</v>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="Z51" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA51" s="4" t="n">
@@ -12126,7 +12126,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="L52" s="4" t="n">
         <v>20</v>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="Z52" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA52" s="4" t="n">
@@ -12309,7 +12309,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="L53" s="4" t="n">
         <v>25</v>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="Z53" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 16, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AA53" s="4" t="n">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -15506,10 +15506,10 @@
         <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M72" s="4" t="n">
         <v>1</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="Z72" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA72" s="4" t="n">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -15687,10 +15687,10 @@
         <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M73" s="4" t="n">
         <v>1</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="Z73" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA73" s="4" t="n">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -15868,10 +15868,10 @@
         <v>1</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>1</v>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="Z74" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA74" s="4" t="n">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -16049,10 +16049,10 @@
         <v>1</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M75" s="4" t="n">
         <v>1</v>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="Z75" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA75" s="4" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -16230,10 +16230,10 @@
         <v>1</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M76" s="4" t="n">
         <v>1</v>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="Z76" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA76" s="4" t="n">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -16411,10 +16411,10 @@
         <v>1</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M77" s="4" t="n">
         <v>1</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="Z77" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA77" s="4" t="n">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -16592,10 +16592,10 @@
         <v>1</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M78" s="4" t="n">
         <v>1</v>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="Z78" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA78" s="4" t="n">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -16773,10 +16773,10 @@
         <v>1</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M79" s="4" t="n">
         <v>1</v>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="Z79" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA79" s="4" t="n">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -16954,10 +16954,10 @@
         <v>1</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M80" s="4" t="n">
         <v>1</v>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="Z80" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA80" s="4" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -17135,10 +17135,10 @@
         <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M81" s="4" t="n">
         <v>1</v>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="Z81" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA81" s="4" t="n">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -17316,10 +17316,10 @@
         <v>1</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>1</v>
@@ -17364,7 +17364,7 @@
       </c>
       <c r="Z82" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA82" s="4" t="n">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -17497,10 +17497,10 @@
         <v>1</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M83" s="4" t="n">
         <v>1</v>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="Z83" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA83" s="4" t="n">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -17678,10 +17678,10 @@
         <v>1</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>1</v>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="Z84" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA84" s="4" t="n">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -17859,10 +17859,10 @@
         <v>1</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M85" s="4" t="n">
         <v>1</v>
@@ -17907,7 +17907,7 @@
       </c>
       <c r="Z85" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA85" s="4" t="n">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -18040,10 +18040,10 @@
         <v>1</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>1</v>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="Z86" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA86" s="4" t="n">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -18221,10 +18221,10 @@
         <v>1</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M87" s="4" t="n">
         <v>1</v>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="Z87" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA87" s="4" t="n">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -18402,10 +18402,10 @@
         <v>1</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M88" s="4" t="n">
         <v>1</v>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="Z88" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA88" s="4" t="n">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -18583,10 +18583,10 @@
         <v>1</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M89" s="4" t="n">
         <v>1</v>
@@ -18631,7 +18631,7 @@
       </c>
       <c r="Z89" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA89" s="4" t="n">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -18764,10 +18764,10 @@
         <v>1</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M90" s="4" t="n">
         <v>1</v>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="Z90" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA90" s="4" t="n">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -18945,10 +18945,10 @@
         <v>1</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>1</v>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="Z91" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA91" s="4" t="n">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -19126,10 +19126,10 @@
         <v>1</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M92" s="4" t="n">
         <v>1</v>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="Z92" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA92" s="4" t="n">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -19307,10 +19307,10 @@
         <v>1</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M93" s="4" t="n">
         <v>1</v>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="Z93" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA93" s="4" t="n">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -19488,10 +19488,10 @@
         <v>1</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M94" s="4" t="n">
         <v>1</v>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="Z94" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA94" s="4" t="n">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -19669,10 +19669,10 @@
         <v>1</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M95" s="4" t="n">
         <v>1</v>
@@ -19717,7 +19717,7 @@
       </c>
       <c r="Z95" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA95" s="4" t="n">
@@ -19838,7 +19838,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -19850,10 +19850,10 @@
         <v>1</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M96" s="4" t="n">
         <v>1</v>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="Z96" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA96" s="4" t="n">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -20031,10 +20031,10 @@
         <v>1</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M97" s="4" t="n">
         <v>1</v>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="Z97" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA97" s="4" t="n">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -20212,10 +20212,10 @@
         <v>1</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M98" s="4" t="n">
         <v>1</v>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="Z98" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA98" s="4" t="n">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -20393,10 +20393,10 @@
         <v>1</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M99" s="4" t="n">
         <v>1</v>
@@ -20441,7 +20441,7 @@
       </c>
       <c r="Z99" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 16, 9, 16]</t>
+          <t>[9, 9, 9, 9, 9]</t>
         </is>
       </c>
       <c r="AA99" s="4" t="n">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>99d89a7c5f512a33d191b68e8d947bca1e44ccbff415bb4d6093eb8767937a70</t>
+          <t>8bacef626a96d12a0eaa598cdc76e23ab4c93913bc3274ac50212bff5b7a1bdd</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -15936,7 +15936,11 @@
           <t>tomb_nave</t>
         </is>
       </c>
-      <c r="R72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S72" s="4" t="n">
         <v>0</v>
       </c>
@@ -16120,7 +16124,11 @@
           <t>tomb_nave</t>
         </is>
       </c>
-      <c r="R73" s="4" t="inlineStr"/>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S73" s="4" t="n">
         <v>0</v>
       </c>
@@ -16304,7 +16312,11 @@
           <t>tomb_nave</t>
         </is>
       </c>
-      <c r="R74" s="4" t="inlineStr"/>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S74" s="4" t="n">
         <v>0</v>
       </c>
@@ -16488,7 +16500,11 @@
           <t>tomb_nave</t>
         </is>
       </c>
-      <c r="R75" s="4" t="inlineStr"/>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S75" s="4" t="n">
         <v>0</v>
       </c>
@@ -16672,7 +16688,11 @@
           <t>tomb_nave</t>
         </is>
       </c>
-      <c r="R76" s="4" t="inlineStr"/>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S76" s="4" t="n">
         <v>0</v>
       </c>
@@ -16854,7 +16874,11 @@
           <t>tomb_nave</t>
         </is>
       </c>
-      <c r="R77" s="4" t="inlineStr"/>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S77" s="4" t="n">
         <v>0</v>
       </c>
@@ -17036,7 +17060,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R78" s="4" t="inlineStr"/>
+      <c r="R78" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S78" s="4" t="n">
         <v>0</v>
       </c>
@@ -17218,7 +17246,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R79" s="4" t="inlineStr"/>
+      <c r="R79" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S79" s="4" t="n">
         <v>0</v>
       </c>
@@ -17400,7 +17432,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R80" s="4" t="inlineStr"/>
+      <c r="R80" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S80" s="4" t="n">
         <v>0</v>
       </c>
@@ -17584,7 +17620,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R81" s="4" t="inlineStr"/>
+      <c r="R81" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S81" s="4" t="n">
         <v>0</v>
       </c>
@@ -17766,7 +17806,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R82" s="4" t="inlineStr"/>
+      <c r="R82" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S82" s="4" t="n">
         <v>0</v>
       </c>
@@ -17948,7 +17992,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R83" s="4" t="inlineStr"/>
+      <c r="R83" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S83" s="4" t="n">
         <v>0</v>
       </c>
@@ -18130,7 +18178,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R84" s="4" t="inlineStr"/>
+      <c r="R84" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S84" s="4" t="n">
         <v>0</v>
       </c>
@@ -18312,7 +18364,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R85" s="4" t="inlineStr"/>
+      <c r="R85" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S85" s="4" t="n">
         <v>0</v>
       </c>
@@ -18494,7 +18550,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R86" s="4" t="inlineStr"/>
+      <c r="R86" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S86" s="4" t="n">
         <v>0</v>
       </c>
@@ -18676,7 +18736,11 @@
           <t>tomb_ossuary</t>
         </is>
       </c>
-      <c r="R87" s="4" t="inlineStr"/>
+      <c r="R87" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S87" s="4" t="n">
         <v>0</v>
       </c>
@@ -18858,7 +18922,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R88" s="4" t="inlineStr"/>
+      <c r="R88" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S88" s="4" t="n">
         <v>0</v>
       </c>
@@ -19042,7 +19110,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R89" s="4" t="inlineStr"/>
+      <c r="R89" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S89" s="4" t="n">
         <v>0</v>
       </c>
@@ -19224,7 +19296,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R90" s="4" t="inlineStr"/>
+      <c r="R90" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S90" s="4" t="n">
         <v>0</v>
       </c>
@@ -19406,7 +19482,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R91" s="4" t="inlineStr"/>
+      <c r="R91" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S91" s="4" t="n">
         <v>0</v>
       </c>
@@ -19588,7 +19668,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R92" s="4" t="inlineStr"/>
+      <c r="R92" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S92" s="4" t="n">
         <v>0</v>
       </c>
@@ -19770,7 +19854,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R93" s="4" t="inlineStr"/>
+      <c r="R93" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S93" s="4" t="n">
         <v>0</v>
       </c>
@@ -19954,7 +20042,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S94" s="4" t="n">
         <v>0</v>
       </c>
@@ -20136,7 +20228,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R95" s="4" t="inlineStr"/>
+      <c r="R95" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S95" s="4" t="n">
         <v>0</v>
       </c>
@@ -20318,7 +20414,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R96" s="4" t="inlineStr"/>
+      <c r="R96" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S96" s="4" t="n">
         <v>0</v>
       </c>
@@ -20500,7 +20600,11 @@
           <t>tomb_crypt</t>
         </is>
       </c>
-      <c r="R97" s="4" t="inlineStr"/>
+      <c r="R97" s="4" t="inlineStr">
+        <is>
+          <t>tomb</t>
+        </is>
+      </c>
       <c r="S97" s="4" t="n">
         <v>0</v>
       </c>
@@ -21664,7 +21768,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>298f72a0c87d7f5e42abeb2941bf37599b53b1a9a3812282a2b7f1a5f22828b8</t>
+          <t>045575118fac6ef03c41077d8d8b6c820d0c503553f00bb64cab8c0f91f2c035</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -15926,11 +15926,7 @@
       <c r="O72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P72" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P72" s="4" t="inlineStr"/>
       <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>tomb_nave</t>
@@ -16114,11 +16110,7 @@
       <c r="O73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P73" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P73" s="4" t="inlineStr"/>
       <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>tomb_nave</t>
@@ -16302,11 +16294,7 @@
       <c r="O74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P74" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P74" s="4" t="inlineStr"/>
       <c r="Q74" s="4" t="inlineStr">
         <is>
           <t>tomb_nave</t>
@@ -16490,11 +16478,7 @@
       <c r="O75" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P75" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P75" s="4" t="inlineStr"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>tomb_nave</t>
@@ -16678,11 +16662,7 @@
       <c r="O76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P76" s="4" t="inlineStr"/>
       <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>tomb_nave</t>
@@ -16864,11 +16844,7 @@
       <c r="O77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P77" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P77" s="4" t="inlineStr"/>
       <c r="Q77" s="4" t="inlineStr">
         <is>
           <t>tomb_nave</t>
@@ -17050,11 +17026,7 @@
       <c r="O78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P78" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P78" s="4" t="inlineStr"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -17236,11 +17208,7 @@
       <c r="O79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P79" s="4" t="inlineStr"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -17422,11 +17390,7 @@
       <c r="O80" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P80" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P80" s="4" t="inlineStr"/>
       <c r="Q80" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -17610,11 +17574,7 @@
       <c r="O81" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P81" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P81" s="4" t="inlineStr"/>
       <c r="Q81" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -17796,11 +17756,7 @@
       <c r="O82" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P82" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P82" s="4" t="inlineStr"/>
       <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -17982,11 +17938,7 @@
       <c r="O83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P83" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P83" s="4" t="inlineStr"/>
       <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -18168,11 +18120,7 @@
       <c r="O84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P84" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P84" s="4" t="inlineStr"/>
       <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -18354,11 +18302,7 @@
       <c r="O85" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P85" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P85" s="4" t="inlineStr"/>
       <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -18540,11 +18484,7 @@
       <c r="O86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P86" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P86" s="4" t="inlineStr"/>
       <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -18726,11 +18666,7 @@
       <c r="O87" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P87" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P87" s="4" t="inlineStr"/>
       <c r="Q87" s="4" t="inlineStr">
         <is>
           <t>tomb_ossuary</t>
@@ -18912,11 +18848,7 @@
       <c r="O88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P88" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P88" s="4" t="inlineStr"/>
       <c r="Q88" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -19100,11 +19032,7 @@
       <c r="O89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P89" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -19286,11 +19214,7 @@
       <c r="O90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P90" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P90" s="4" t="inlineStr"/>
       <c r="Q90" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -19472,11 +19396,7 @@
       <c r="O91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P91" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P91" s="4" t="inlineStr"/>
       <c r="Q91" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -19658,11 +19578,7 @@
       <c r="O92" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P92" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P92" s="4" t="inlineStr"/>
       <c r="Q92" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -19844,11 +19760,7 @@
       <c r="O93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P93" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P93" s="4" t="inlineStr"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -20032,11 +19944,7 @@
       <c r="O94" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P94" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P94" s="4" t="inlineStr"/>
       <c r="Q94" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -20218,11 +20126,7 @@
       <c r="O95" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P95" s="4" t="inlineStr"/>
       <c r="Q95" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -20404,11 +20308,7 @@
       <c r="O96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P96" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P96" s="4" t="inlineStr"/>
       <c r="Q96" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -20590,11 +20490,7 @@
       <c r="O97" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P97" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P97" s="4" t="inlineStr"/>
       <c r="Q97" s="4" t="inlineStr">
         <is>
           <t>tomb_crypt</t>
@@ -20776,11 +20672,7 @@
       <c r="O98" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P98" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P98" s="4" t="inlineStr"/>
       <c r="Q98" s="4" t="inlineStr">
         <is>
           <t>belisar_thronehall</t>
@@ -20958,11 +20850,7 @@
       <c r="O99" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P99" s="4" t="inlineStr">
-        <is>
-          <t>se_enemy_roardeer</t>
-        </is>
-      </c>
+      <c r="P99" s="4" t="inlineStr"/>
       <c r="Q99" s="4" t="inlineStr">
         <is>
           <t>belisar_thronehall</t>
@@ -21768,7 +21656,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>045575118fac6ef03c41077d8d8b6c820d0c503553f00bb64cab8c0f91f2c035</t>
+          <t>7066a681f4922c878ac2b04d6472de10fc9ee2684f1895a09694c2bd09c7fef5</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -1027,7 +1027,7 @@
       <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="895350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1052,7 +1052,7 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="866775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -2595,6 +2595,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2887,7 +2937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ100"/>
+  <dimension ref="A1:BK102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2937,21 +2987,22 @@
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="16" customWidth="1" min="46" max="46"/>
     <col width="7" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="15" customWidth="1" min="49" max="49"/>
-    <col width="21" customWidth="1" min="50" max="50"/>
-    <col width="7" customWidth="1" min="51" max="51"/>
+    <col width="8" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="21" customWidth="1" min="51" max="51"/>
     <col width="7" customWidth="1" min="52" max="52"/>
-    <col width="16" customWidth="1" min="53" max="53"/>
-    <col width="7" customWidth="1" min="54" max="54"/>
+    <col width="7" customWidth="1" min="53" max="53"/>
+    <col width="16" customWidth="1" min="54" max="54"/>
     <col width="7" customWidth="1" min="55" max="55"/>
-    <col width="18" customWidth="1" min="56" max="56"/>
-    <col width="7" customWidth="1" min="57" max="57"/>
+    <col width="7" customWidth="1" min="56" max="56"/>
+    <col width="18" customWidth="1" min="57" max="57"/>
     <col width="7" customWidth="1" min="58" max="58"/>
-    <col width="17" customWidth="1" min="59" max="59"/>
-    <col width="7" customWidth="1" min="60" max="60"/>
+    <col width="7" customWidth="1" min="59" max="59"/>
+    <col width="17" customWidth="1" min="60" max="60"/>
     <col width="7" customWidth="1" min="61" max="61"/>
     <col width="7" customWidth="1" min="62" max="62"/>
+    <col width="7" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3042,18 +3093,18 @@
       <c r="AS1" s="1" t="n"/>
       <c r="AT1" s="1" t="n"/>
       <c r="AU1" s="1" t="n"/>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="n"/>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>圖幅</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="n"/>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="n"/>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>掉落</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="n"/>
       <c r="AZ1" s="1" t="n"/>
       <c r="BA1" s="1" t="n"/>
       <c r="BB1" s="1" t="n"/>
@@ -3064,7 +3115,8 @@
       <c r="BG1" s="1" t="n"/>
       <c r="BH1" s="1" t="n"/>
       <c r="BI1" s="1" t="n"/>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="n"/>
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
@@ -3304,75 +3356,80 @@
       </c>
       <c r="AV2" s="2" t="inlineStr">
         <is>
+          <t>hitFxCd</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
           <t>fit.mode</t>
         </is>
       </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>fit.pos</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>loot1.id</t>
         </is>
       </c>
-      <c r="AY2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>loot1.n</t>
         </is>
       </c>
-      <c r="AZ2" s="2" t="inlineStr">
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>loot1.p</t>
         </is>
       </c>
-      <c r="BA2" s="2" t="inlineStr">
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>loot2.id</t>
         </is>
       </c>
-      <c r="BB2" s="2" t="inlineStr">
+      <c r="BC2" s="2" t="inlineStr">
         <is>
           <t>loot2.n</t>
         </is>
       </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>loot2.p</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr">
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>loot3.id</t>
         </is>
       </c>
-      <c r="BE2" s="2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>loot3.n</t>
         </is>
       </c>
-      <c r="BF2" s="2" t="inlineStr">
+      <c r="BG2" s="2" t="inlineStr">
         <is>
           <t>loot3.p</t>
         </is>
       </c>
-      <c r="BG2" s="2" t="inlineStr">
+      <c r="BH2" s="2" t="inlineStr">
         <is>
           <t>loot4.id</t>
         </is>
       </c>
-      <c r="BH2" s="2" t="inlineStr">
+      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>loot4.n</t>
         </is>
       </c>
-      <c r="BI2" s="2" t="inlineStr">
+      <c r="BJ2" s="2" t="inlineStr">
         <is>
           <t>loot4.p</t>
         </is>
       </c>
-      <c r="BJ2" s="2" t="inlineStr">
+      <c r="BK2" s="2" t="inlineStr">
         <is>
           <t>special</t>
         </is>
@@ -3608,75 +3665,80 @@
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
+          <t>CD秒</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
           <t>取景模式</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>取景位置</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <t>掉落1</t>
         </is>
       </c>
-      <c r="AY3" s="3" t="inlineStr">
+      <c r="AZ3" s="3" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
-      <c r="AZ3" s="3" t="inlineStr">
+      <c r="BA3" s="3" t="inlineStr">
         <is>
           <t>機率</t>
         </is>
       </c>
-      <c r="BA3" s="3" t="inlineStr">
+      <c r="BB3" s="3" t="inlineStr">
         <is>
           <t>掉落2</t>
         </is>
       </c>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr">
         <is>
           <t>機率</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr">
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>掉落3</t>
         </is>
       </c>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>機率</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BH3" s="3" t="inlineStr">
         <is>
           <t>掉落4</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr">
+      <c r="BI3" s="3" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
-      <c r="BI3" s="3" t="inlineStr">
+      <c r="BJ3" s="3" t="inlineStr">
         <is>
           <t>機率</t>
         </is>
       </c>
-      <c r="BJ3" s="3" t="inlineStr">
+      <c r="BK3" s="3" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
@@ -3844,7 +3906,8 @@
       <c r="BG4" s="4" t="inlineStr"/>
       <c r="BH4" s="4" t="inlineStr"/>
       <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr">
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4004,7 +4067,8 @@
       <c r="BG5" s="4" t="inlineStr"/>
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr">
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4162,7 +4226,8 @@
       <c r="BG6" s="4" t="inlineStr"/>
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr">
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4320,7 +4385,8 @@
       <c r="BG7" s="4" t="inlineStr"/>
       <c r="BH7" s="4" t="inlineStr"/>
       <c r="BI7" s="4" t="inlineStr"/>
-      <c r="BJ7" s="4" t="inlineStr">
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4475,12 +4541,12 @@
       </c>
       <c r="AU8" s="4" t="inlineStr"/>
       <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr">
         <is>
           <t>62% 78%</t>
         </is>
       </c>
-      <c r="AX8" s="4" t="inlineStr"/>
       <c r="AY8" s="4" t="inlineStr"/>
       <c r="AZ8" s="4" t="inlineStr"/>
       <c r="BA8" s="4" t="inlineStr"/>
@@ -4492,7 +4558,8 @@
       <c r="BG8" s="4" t="inlineStr"/>
       <c r="BH8" s="4" t="inlineStr"/>
       <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr">
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4651,12 +4718,12 @@
       </c>
       <c r="AU9" s="4" t="inlineStr"/>
       <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
+      <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AX9" s="4" t="inlineStr">
         <is>
           <t>50% 30%</t>
         </is>
       </c>
-      <c r="AX9" s="4" t="inlineStr"/>
       <c r="AY9" s="4" t="inlineStr"/>
       <c r="AZ9" s="4" t="inlineStr"/>
       <c r="BA9" s="4" t="inlineStr"/>
@@ -4668,7 +4735,8 @@
       <c r="BG9" s="4" t="inlineStr"/>
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
-      <c r="BJ9" s="4" t="inlineStr">
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4823,12 +4891,12 @@
       </c>
       <c r="AU10" s="4" t="inlineStr"/>
       <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
+      <c r="AW10" s="4" t="inlineStr"/>
+      <c r="AX10" s="4" t="inlineStr">
         <is>
           <t>50% 30%</t>
         </is>
       </c>
-      <c r="AX10" s="4" t="inlineStr"/>
       <c r="AY10" s="4" t="inlineStr"/>
       <c r="AZ10" s="4" t="inlineStr"/>
       <c r="BA10" s="4" t="inlineStr"/>
@@ -4840,7 +4908,8 @@
       <c r="BG10" s="4" t="inlineStr"/>
       <c r="BH10" s="4" t="inlineStr"/>
       <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr">
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -4992,7 +5061,8 @@
       <c r="BG11" s="4" t="inlineStr"/>
       <c r="BH11" s="4" t="inlineStr"/>
       <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr">
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -5156,7 +5226,8 @@
       <c r="BG12" s="4" t="inlineStr"/>
       <c r="BH12" s="4" t="inlineStr"/>
       <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr">
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -5306,17 +5377,17 @@
         </is>
       </c>
       <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr">
+      <c r="AV13" s="4" t="inlineStr"/>
+      <c r="AW13" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW13" s="4" t="inlineStr">
+      <c r="AX13" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX13" s="4" t="inlineStr"/>
       <c r="AY13" s="4" t="inlineStr"/>
       <c r="AZ13" s="4" t="inlineStr"/>
       <c r="BA13" s="4" t="inlineStr"/>
@@ -5328,7 +5399,8 @@
       <c r="BG13" s="4" t="inlineStr"/>
       <c r="BH13" s="4" t="inlineStr"/>
       <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr">
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -5484,17 +5556,17 @@
         </is>
       </c>
       <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr">
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW14" s="4" t="inlineStr">
+      <c r="AX14" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX14" s="4" t="inlineStr"/>
       <c r="AY14" s="4" t="inlineStr"/>
       <c r="AZ14" s="4" t="inlineStr"/>
       <c r="BA14" s="4" t="inlineStr"/>
@@ -5506,7 +5578,8 @@
       <c r="BG14" s="4" t="inlineStr"/>
       <c r="BH14" s="4" t="inlineStr"/>
       <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr">
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -5662,17 +5735,17 @@
         </is>
       </c>
       <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr">
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW15" s="4" t="inlineStr">
+      <c r="AX15" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX15" s="4" t="inlineStr"/>
       <c r="AY15" s="4" t="inlineStr"/>
       <c r="AZ15" s="4" t="inlineStr"/>
       <c r="BA15" s="4" t="inlineStr"/>
@@ -5684,7 +5757,8 @@
       <c r="BG15" s="4" t="inlineStr"/>
       <c r="BH15" s="4" t="inlineStr"/>
       <c r="BI15" s="4" t="inlineStr"/>
-      <c r="BJ15" s="4" t="inlineStr">
+      <c r="BJ15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -5840,17 +5914,17 @@
         </is>
       </c>
       <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr">
+      <c r="AV16" s="4" t="inlineStr"/>
+      <c r="AW16" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW16" s="4" t="inlineStr">
+      <c r="AX16" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX16" s="4" t="inlineStr"/>
       <c r="AY16" s="4" t="inlineStr"/>
       <c r="AZ16" s="4" t="inlineStr"/>
       <c r="BA16" s="4" t="inlineStr"/>
@@ -5862,7 +5936,8 @@
       <c r="BG16" s="4" t="inlineStr"/>
       <c r="BH16" s="4" t="inlineStr"/>
       <c r="BI16" s="4" t="inlineStr"/>
-      <c r="BJ16" s="4" t="inlineStr">
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -6018,17 +6093,17 @@
         </is>
       </c>
       <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr">
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW17" s="4" t="inlineStr">
+      <c r="AX17" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX17" s="4" t="inlineStr"/>
       <c r="AY17" s="4" t="inlineStr"/>
       <c r="AZ17" s="4" t="inlineStr"/>
       <c r="BA17" s="4" t="inlineStr"/>
@@ -6040,7 +6115,8 @@
       <c r="BG17" s="4" t="inlineStr"/>
       <c r="BH17" s="4" t="inlineStr"/>
       <c r="BI17" s="4" t="inlineStr"/>
-      <c r="BJ17" s="4" t="inlineStr">
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -6198,17 +6274,17 @@
         </is>
       </c>
       <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr">
+      <c r="AV18" s="4" t="inlineStr"/>
+      <c r="AW18" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW18" s="4" t="inlineStr">
+      <c r="AX18" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX18" s="4" t="inlineStr"/>
       <c r="AY18" s="4" t="inlineStr"/>
       <c r="AZ18" s="4" t="inlineStr"/>
       <c r="BA18" s="4" t="inlineStr"/>
@@ -6220,7 +6296,8 @@
       <c r="BG18" s="4" t="inlineStr"/>
       <c r="BH18" s="4" t="inlineStr"/>
       <c r="BI18" s="4" t="inlineStr"/>
-      <c r="BJ18" s="4" t="inlineStr">
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -6390,7 +6467,8 @@
       <c r="BG19" s="4" t="inlineStr"/>
       <c r="BH19" s="4" t="inlineStr"/>
       <c r="BI19" s="4" t="inlineStr"/>
-      <c r="BJ19" s="4" t="inlineStr">
+      <c r="BJ19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -6546,17 +6624,17 @@
         </is>
       </c>
       <c r="AU20" s="4" t="inlineStr"/>
-      <c r="AV20" s="4" t="inlineStr">
+      <c r="AV20" s="4" t="inlineStr"/>
+      <c r="AW20" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW20" s="4" t="inlineStr">
+      <c r="AX20" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX20" s="4" t="inlineStr"/>
       <c r="AY20" s="4" t="inlineStr"/>
       <c r="AZ20" s="4" t="inlineStr"/>
       <c r="BA20" s="4" t="inlineStr"/>
@@ -6568,7 +6646,8 @@
       <c r="BG20" s="4" t="inlineStr"/>
       <c r="BH20" s="4" t="inlineStr"/>
       <c r="BI20" s="4" t="inlineStr"/>
-      <c r="BJ20" s="4" t="inlineStr">
+      <c r="BJ20" s="4" t="inlineStr"/>
+      <c r="BK20" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -6724,17 +6803,17 @@
         </is>
       </c>
       <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr">
+      <c r="AV21" s="4" t="inlineStr"/>
+      <c r="AW21" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW21" s="4" t="inlineStr">
+      <c r="AX21" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX21" s="4" t="inlineStr"/>
       <c r="AY21" s="4" t="inlineStr"/>
       <c r="AZ21" s="4" t="inlineStr"/>
       <c r="BA21" s="4" t="inlineStr"/>
@@ -6746,7 +6825,8 @@
       <c r="BG21" s="4" t="inlineStr"/>
       <c r="BH21" s="4" t="inlineStr"/>
       <c r="BI21" s="4" t="inlineStr"/>
-      <c r="BJ21" s="4" t="inlineStr">
+      <c r="BJ21" s="4" t="inlineStr"/>
+      <c r="BK21" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -6902,17 +6982,17 @@
         </is>
       </c>
       <c r="AU22" s="4" t="inlineStr"/>
-      <c r="AV22" s="4" t="inlineStr">
+      <c r="AV22" s="4" t="inlineStr"/>
+      <c r="AW22" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW22" s="4" t="inlineStr">
+      <c r="AX22" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX22" s="4" t="inlineStr"/>
       <c r="AY22" s="4" t="inlineStr"/>
       <c r="AZ22" s="4" t="inlineStr"/>
       <c r="BA22" s="4" t="inlineStr"/>
@@ -6924,7 +7004,8 @@
       <c r="BG22" s="4" t="inlineStr"/>
       <c r="BH22" s="4" t="inlineStr"/>
       <c r="BI22" s="4" t="inlineStr"/>
-      <c r="BJ22" s="4" t="inlineStr">
+      <c r="BJ22" s="4" t="inlineStr"/>
+      <c r="BK22" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -7080,17 +7161,17 @@
         </is>
       </c>
       <c r="AU23" s="4" t="inlineStr"/>
-      <c r="AV23" s="4" t="inlineStr">
+      <c r="AV23" s="4" t="inlineStr"/>
+      <c r="AW23" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW23" s="4" t="inlineStr">
+      <c r="AX23" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX23" s="4" t="inlineStr"/>
       <c r="AY23" s="4" t="inlineStr"/>
       <c r="AZ23" s="4" t="inlineStr"/>
       <c r="BA23" s="4" t="inlineStr"/>
@@ -7102,7 +7183,8 @@
       <c r="BG23" s="4" t="inlineStr"/>
       <c r="BH23" s="4" t="inlineStr"/>
       <c r="BI23" s="4" t="inlineStr"/>
-      <c r="BJ23" s="4" t="inlineStr">
+      <c r="BJ23" s="4" t="inlineStr"/>
+      <c r="BK23" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -7258,17 +7340,17 @@
         </is>
       </c>
       <c r="AU24" s="4" t="inlineStr"/>
-      <c r="AV24" s="4" t="inlineStr">
+      <c r="AV24" s="4" t="inlineStr"/>
+      <c r="AW24" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW24" s="4" t="inlineStr">
+      <c r="AX24" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX24" s="4" t="inlineStr"/>
       <c r="AY24" s="4" t="inlineStr"/>
       <c r="AZ24" s="4" t="inlineStr"/>
       <c r="BA24" s="4" t="inlineStr"/>
@@ -7280,7 +7362,8 @@
       <c r="BG24" s="4" t="inlineStr"/>
       <c r="BH24" s="4" t="inlineStr"/>
       <c r="BI24" s="4" t="inlineStr"/>
-      <c r="BJ24" s="4" t="inlineStr">
+      <c r="BJ24" s="4" t="inlineStr"/>
+      <c r="BK24" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -7438,17 +7521,17 @@
         </is>
       </c>
       <c r="AU25" s="4" t="inlineStr"/>
-      <c r="AV25" s="4" t="inlineStr">
+      <c r="AV25" s="4" t="inlineStr"/>
+      <c r="AW25" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW25" s="4" t="inlineStr">
+      <c r="AX25" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX25" s="4" t="inlineStr"/>
       <c r="AY25" s="4" t="inlineStr"/>
       <c r="AZ25" s="4" t="inlineStr"/>
       <c r="BA25" s="4" t="inlineStr"/>
@@ -7460,7 +7543,8 @@
       <c r="BG25" s="4" t="inlineStr"/>
       <c r="BH25" s="4" t="inlineStr"/>
       <c r="BI25" s="4" t="inlineStr"/>
-      <c r="BJ25" s="4" t="inlineStr">
+      <c r="BJ25" s="4" t="inlineStr"/>
+      <c r="BK25" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -7614,25 +7698,25 @@
         </is>
       </c>
       <c r="AU26" s="4" t="inlineStr"/>
-      <c r="AV26" s="4" t="inlineStr">
+      <c r="AV26" s="4" t="inlineStr"/>
+      <c r="AW26" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW26" s="4" t="inlineStr">
+      <c r="AX26" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX26" s="4" t="inlineStr">
+      <c r="AY26" s="4" t="inlineStr">
         <is>
           <t>黃銅彈殼｜brass_casing</t>
         </is>
       </c>
-      <c r="AY26" s="4" t="n">
+      <c r="AZ26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AZ26" s="4" t="inlineStr"/>
       <c r="BA26" s="4" t="inlineStr"/>
       <c r="BB26" s="4" t="inlineStr"/>
       <c r="BC26" s="4" t="inlineStr"/>
@@ -7642,7 +7726,8 @@
       <c r="BG26" s="4" t="inlineStr"/>
       <c r="BH26" s="4" t="inlineStr"/>
       <c r="BI26" s="4" t="inlineStr"/>
-      <c r="BJ26" s="4" t="inlineStr">
+      <c r="BJ26" s="4" t="inlineStr"/>
+      <c r="BK26" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -7796,25 +7881,25 @@
         </is>
       </c>
       <c r="AU27" s="4" t="inlineStr"/>
-      <c r="AV27" s="4" t="inlineStr">
+      <c r="AV27" s="4" t="inlineStr"/>
+      <c r="AW27" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW27" s="4" t="inlineStr">
+      <c r="AX27" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX27" s="4" t="inlineStr">
+      <c r="AY27" s="4" t="inlineStr">
         <is>
           <t>黃銅彈殼｜brass_casing</t>
         </is>
       </c>
-      <c r="AY27" s="4" t="n">
+      <c r="AZ27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AZ27" s="4" t="inlineStr"/>
       <c r="BA27" s="4" t="inlineStr"/>
       <c r="BB27" s="4" t="inlineStr"/>
       <c r="BC27" s="4" t="inlineStr"/>
@@ -7824,7 +7909,8 @@
       <c r="BG27" s="4" t="inlineStr"/>
       <c r="BH27" s="4" t="inlineStr"/>
       <c r="BI27" s="4" t="inlineStr"/>
-      <c r="BJ27" s="4" t="inlineStr">
+      <c r="BJ27" s="4" t="inlineStr"/>
+      <c r="BK27" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -7988,51 +8074,52 @@
       <c r="AU28" s="4" t="inlineStr"/>
       <c r="AV28" s="4" t="inlineStr"/>
       <c r="AW28" s="4" t="inlineStr"/>
-      <c r="AX28" s="4" t="inlineStr">
+      <c r="AX28" s="4" t="inlineStr"/>
+      <c r="AY28" s="4" t="inlineStr">
         <is>
           <t>毒牙｜venom_fang</t>
         </is>
       </c>
-      <c r="AY28" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA28" s="4" t="inlineStr">
+      <c r="BB28" s="4" t="inlineStr">
         <is>
           <t>毒爪｜venom_claw</t>
         </is>
       </c>
-      <c r="BB28" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="BC28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD28" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="BD28" s="4" t="inlineStr">
+      <c r="BE28" s="4" t="inlineStr">
         <is>
           <t>飛翅｜chitin_wing</t>
         </is>
       </c>
-      <c r="BE28" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="BF28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG28" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BG28" s="4" t="inlineStr">
+      <c r="BH28" s="4" t="inlineStr">
         <is>
           <t>殼甲｜chitin_shell</t>
         </is>
       </c>
-      <c r="BH28" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="BI28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ28" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="BJ28" s="4" t="inlineStr">
+      <c r="BK28" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8196,43 +8283,44 @@
       <c r="AU29" s="4" t="inlineStr"/>
       <c r="AV29" s="4" t="inlineStr"/>
       <c r="AW29" s="4" t="inlineStr"/>
-      <c r="AX29" s="4" t="inlineStr">
+      <c r="AX29" s="4" t="inlineStr"/>
+      <c r="AY29" s="4" t="inlineStr">
         <is>
           <t>毒牙｜venom_fang</t>
         </is>
       </c>
-      <c r="AY29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA29" s="4" t="inlineStr">
+      <c r="BB29" s="4" t="inlineStr">
         <is>
           <t>蒼鱗｜azure_scale</t>
         </is>
       </c>
-      <c r="BB29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="BC29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD29" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="BD29" s="4" t="inlineStr">
+      <c r="BE29" s="4" t="inlineStr">
         <is>
           <t>蒼羽｜azure_feather</t>
         </is>
       </c>
-      <c r="BE29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="BF29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG29" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="BG29" s="4" t="inlineStr"/>
       <c r="BH29" s="4" t="inlineStr"/>
       <c r="BI29" s="4" t="inlineStr"/>
-      <c r="BJ29" s="4" t="inlineStr">
+      <c r="BJ29" s="4" t="inlineStr"/>
+      <c r="BK29" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8396,18 +8484,18 @@
       <c r="AU30" s="4" t="inlineStr"/>
       <c r="AV30" s="4" t="inlineStr"/>
       <c r="AW30" s="4" t="inlineStr"/>
-      <c r="AX30" s="4" t="inlineStr">
+      <c r="AX30" s="4" t="inlineStr"/>
+      <c r="AY30" s="4" t="inlineStr">
         <is>
           <t>黃銅彈殼｜brass_casing</t>
         </is>
       </c>
-      <c r="AY30" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA30" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="BA30" s="4" t="inlineStr"/>
       <c r="BB30" s="4" t="inlineStr"/>
       <c r="BC30" s="4" t="inlineStr"/>
       <c r="BD30" s="4" t="inlineStr"/>
@@ -8416,7 +8504,8 @@
       <c r="BG30" s="4" t="inlineStr"/>
       <c r="BH30" s="4" t="inlineStr"/>
       <c r="BI30" s="4" t="inlineStr"/>
-      <c r="BJ30" s="4" t="inlineStr">
+      <c r="BJ30" s="4" t="inlineStr"/>
+      <c r="BK30" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8572,25 +8661,25 @@
         </is>
       </c>
       <c r="AU31" s="4" t="inlineStr"/>
-      <c r="AV31" s="4" t="inlineStr">
+      <c r="AV31" s="4" t="inlineStr"/>
+      <c r="AW31" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW31" s="4" t="inlineStr">
+      <c r="AX31" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX31" s="4" t="inlineStr">
+      <c r="AY31" s="4" t="inlineStr">
         <is>
           <t>山貓腿肉｜meat_lynx</t>
         </is>
       </c>
-      <c r="AY31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ31" s="4" t="inlineStr"/>
+      <c r="AZ31" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA31" s="4" t="inlineStr"/>
       <c r="BB31" s="4" t="inlineStr"/>
       <c r="BC31" s="4" t="inlineStr"/>
@@ -8600,7 +8689,8 @@
       <c r="BG31" s="4" t="inlineStr"/>
       <c r="BH31" s="4" t="inlineStr"/>
       <c r="BI31" s="4" t="inlineStr"/>
-      <c r="BJ31" s="4" t="inlineStr">
+      <c r="BJ31" s="4" t="inlineStr"/>
+      <c r="BK31" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8756,25 +8846,25 @@
         </is>
       </c>
       <c r="AU32" s="4" t="inlineStr"/>
-      <c r="AV32" s="4" t="inlineStr">
+      <c r="AV32" s="4" t="inlineStr"/>
+      <c r="AW32" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW32" s="4" t="inlineStr">
+      <c r="AX32" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX32" s="4" t="inlineStr">
+      <c r="AY32" s="4" t="inlineStr">
         <is>
           <t>蛇肉｜meat_snake</t>
         </is>
       </c>
-      <c r="AY32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ32" s="4" t="inlineStr"/>
+      <c r="AZ32" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA32" s="4" t="inlineStr"/>
       <c r="BB32" s="4" t="inlineStr"/>
       <c r="BC32" s="4" t="inlineStr"/>
@@ -8784,7 +8874,8 @@
       <c r="BG32" s="4" t="inlineStr"/>
       <c r="BH32" s="4" t="inlineStr"/>
       <c r="BI32" s="4" t="inlineStr"/>
-      <c r="BJ32" s="4" t="inlineStr">
+      <c r="BJ32" s="4" t="inlineStr"/>
+      <c r="BK32" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8940,25 +9031,25 @@
         </is>
       </c>
       <c r="AU33" s="4" t="inlineStr"/>
-      <c r="AV33" s="4" t="inlineStr">
+      <c r="AV33" s="4" t="inlineStr"/>
+      <c r="AW33" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW33" s="4" t="inlineStr">
+      <c r="AX33" s="4" t="inlineStr">
         <is>
           <t>center 70%</t>
         </is>
       </c>
-      <c r="AX33" s="4" t="inlineStr">
+      <c r="AY33" s="4" t="inlineStr">
         <is>
           <t>山豬腹肉｜meat_boar</t>
         </is>
       </c>
-      <c r="AY33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ33" s="4" t="inlineStr"/>
+      <c r="AZ33" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA33" s="4" t="inlineStr"/>
       <c r="BB33" s="4" t="inlineStr"/>
       <c r="BC33" s="4" t="inlineStr"/>
@@ -8968,7 +9059,8 @@
       <c r="BG33" s="4" t="inlineStr"/>
       <c r="BH33" s="4" t="inlineStr"/>
       <c r="BI33" s="4" t="inlineStr"/>
-      <c r="BJ33" s="4" t="inlineStr">
+      <c r="BJ33" s="4" t="inlineStr"/>
+      <c r="BK33" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -9124,28 +9216,28 @@
         </is>
       </c>
       <c r="AU34" s="4" t="inlineStr"/>
-      <c r="AV34" s="4" t="inlineStr">
+      <c r="AV34" s="4" t="inlineStr"/>
+      <c r="AW34" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW34" s="4" t="inlineStr">
+      <c r="AX34" s="4" t="inlineStr">
         <is>
           <t>center 55%</t>
         </is>
       </c>
-      <c r="AX34" s="4" t="inlineStr">
+      <c r="AY34" s="4" t="inlineStr">
         <is>
           <t>虎王的獨角｜tiger_horn</t>
         </is>
       </c>
-      <c r="AY34" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA34" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="BA34" s="4" t="inlineStr"/>
       <c r="BB34" s="4" t="inlineStr"/>
       <c r="BC34" s="4" t="inlineStr"/>
       <c r="BD34" s="4" t="inlineStr"/>
@@ -9154,7 +9246,8 @@
       <c r="BG34" s="4" t="inlineStr"/>
       <c r="BH34" s="4" t="inlineStr"/>
       <c r="BI34" s="4" t="inlineStr"/>
-      <c r="BJ34" s="4" t="inlineStr">
+      <c r="BJ34" s="4" t="inlineStr"/>
+      <c r="BK34" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -9310,25 +9403,25 @@
         </is>
       </c>
       <c r="AU35" s="4" t="inlineStr"/>
-      <c r="AV35" s="4" t="inlineStr">
+      <c r="AV35" s="4" t="inlineStr"/>
+      <c r="AW35" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW35" s="4" t="inlineStr">
+      <c r="AX35" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX35" s="4" t="inlineStr">
+      <c r="AY35" s="4" t="inlineStr">
         <is>
           <t>尖喙｜crow_beak</t>
         </is>
       </c>
-      <c r="AY35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ35" s="4" t="inlineStr"/>
+      <c r="AZ35" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA35" s="4" t="inlineStr"/>
       <c r="BB35" s="4" t="inlineStr"/>
       <c r="BC35" s="4" t="inlineStr"/>
@@ -9338,7 +9431,8 @@
       <c r="BG35" s="4" t="inlineStr"/>
       <c r="BH35" s="4" t="inlineStr"/>
       <c r="BI35" s="4" t="inlineStr"/>
-      <c r="BJ35" s="4" t="inlineStr">
+      <c r="BJ35" s="4" t="inlineStr"/>
+      <c r="BK35" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -9494,25 +9588,25 @@
         </is>
       </c>
       <c r="AU36" s="4" t="inlineStr"/>
-      <c r="AV36" s="4" t="inlineStr">
+      <c r="AV36" s="4" t="inlineStr"/>
+      <c r="AW36" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW36" s="4" t="inlineStr">
+      <c r="AX36" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX36" s="4" t="inlineStr">
+      <c r="AY36" s="4" t="inlineStr">
         <is>
           <t>精靈鹿角｜elf_antler</t>
         </is>
       </c>
-      <c r="AY36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ36" s="4" t="inlineStr"/>
+      <c r="AZ36" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA36" s="4" t="inlineStr"/>
       <c r="BB36" s="4" t="inlineStr"/>
       <c r="BC36" s="4" t="inlineStr"/>
@@ -9522,7 +9616,8 @@
       <c r="BG36" s="4" t="inlineStr"/>
       <c r="BH36" s="4" t="inlineStr"/>
       <c r="BI36" s="4" t="inlineStr"/>
-      <c r="BJ36" s="4" t="inlineStr">
+      <c r="BJ36" s="4" t="inlineStr"/>
+      <c r="BK36" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -9588,7 +9683,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>se_enemy_roardeer</t>
+          <t>sfx_saint</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -9682,17 +9777,17 @@
         </is>
       </c>
       <c r="AU37" s="4" t="inlineStr"/>
-      <c r="AV37" s="4" t="inlineStr">
+      <c r="AV37" s="4" t="inlineStr"/>
+      <c r="AW37" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW37" s="4" t="inlineStr">
+      <c r="AX37" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX37" s="4" t="inlineStr"/>
       <c r="AY37" s="4" t="inlineStr"/>
       <c r="AZ37" s="4" t="inlineStr"/>
       <c r="BA37" s="4" t="inlineStr"/>
@@ -9704,13 +9799,14 @@
       <c r="BG37" s="4" t="inlineStr"/>
       <c r="BH37" s="4" t="inlineStr"/>
       <c r="BI37" s="4" t="inlineStr"/>
-      <c r="BJ37" s="4" t="inlineStr">
+      <c r="BJ37" s="4" t="inlineStr"/>
+      <c r="BK37" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="74.88" customHeight="1">
+    <row r="38" ht="73.32000000000001" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>034</t>
@@ -9770,7 +9866,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>se_enemy_roardeer</t>
+          <t>sfx_saint</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
@@ -9866,17 +9962,17 @@
         </is>
       </c>
       <c r="AU38" s="4" t="inlineStr"/>
-      <c r="AV38" s="4" t="inlineStr">
+      <c r="AV38" s="4" t="inlineStr"/>
+      <c r="AW38" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW38" s="4" t="inlineStr">
+      <c r="AX38" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX38" s="4" t="inlineStr"/>
       <c r="AY38" s="4" t="inlineStr"/>
       <c r="AZ38" s="4" t="inlineStr"/>
       <c r="BA38" s="4" t="inlineStr"/>
@@ -9888,13 +9984,14 @@
       <c r="BG38" s="4" t="inlineStr"/>
       <c r="BH38" s="4" t="inlineStr"/>
       <c r="BI38" s="4" t="inlineStr"/>
-      <c r="BJ38" s="4" t="inlineStr">
+      <c r="BJ38" s="4" t="inlineStr"/>
+      <c r="BK38" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="74.88" customHeight="1">
+    <row r="39" ht="70.98" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>035</t>
@@ -9954,7 +10051,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>se_enemy_roardeer</t>
+          <t>sfx_saint</t>
         </is>
       </c>
       <c r="Q39" s="4" t="inlineStr">
@@ -10048,17 +10145,17 @@
         </is>
       </c>
       <c r="AU39" s="4" t="inlineStr"/>
-      <c r="AV39" s="4" t="inlineStr">
+      <c r="AV39" s="4" t="inlineStr"/>
+      <c r="AW39" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW39" s="4" t="inlineStr">
+      <c r="AX39" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX39" s="4" t="inlineStr"/>
       <c r="AY39" s="4" t="inlineStr"/>
       <c r="AZ39" s="4" t="inlineStr"/>
       <c r="BA39" s="4" t="inlineStr"/>
@@ -10070,7 +10167,8 @@
       <c r="BG39" s="4" t="inlineStr"/>
       <c r="BH39" s="4" t="inlineStr"/>
       <c r="BI39" s="4" t="inlineStr"/>
-      <c r="BJ39" s="4" t="inlineStr">
+      <c r="BJ39" s="4" t="inlineStr"/>
+      <c r="BK39" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10136,7 +10234,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>se_enemy_roardeer</t>
+          <t>sfx_saint</t>
         </is>
       </c>
       <c r="Q40" s="4" t="inlineStr">
@@ -10230,17 +10328,17 @@
         </is>
       </c>
       <c r="AU40" s="4" t="inlineStr"/>
-      <c r="AV40" s="4" t="inlineStr">
+      <c r="AV40" s="4" t="inlineStr"/>
+      <c r="AW40" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW40" s="4" t="inlineStr">
+      <c r="AX40" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX40" s="4" t="inlineStr"/>
       <c r="AY40" s="4" t="inlineStr"/>
       <c r="AZ40" s="4" t="inlineStr"/>
       <c r="BA40" s="4" t="inlineStr"/>
@@ -10252,7 +10350,8 @@
       <c r="BG40" s="4" t="inlineStr"/>
       <c r="BH40" s="4" t="inlineStr"/>
       <c r="BI40" s="4" t="inlineStr"/>
-      <c r="BJ40" s="4" t="inlineStr">
+      <c r="BJ40" s="4" t="inlineStr"/>
+      <c r="BK40" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10408,25 +10507,25 @@
         </is>
       </c>
       <c r="AU41" s="4" t="inlineStr"/>
-      <c r="AV41" s="4" t="inlineStr">
+      <c r="AV41" s="4" t="inlineStr"/>
+      <c r="AW41" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW41" s="4" t="inlineStr">
+      <c r="AX41" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX41" s="4" t="inlineStr">
+      <c r="AY41" s="4" t="inlineStr">
         <is>
           <t>熊掌｜paw_bear</t>
         </is>
       </c>
-      <c r="AY41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ41" s="4" t="inlineStr"/>
+      <c r="AZ41" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA41" s="4" t="inlineStr"/>
       <c r="BB41" s="4" t="inlineStr"/>
       <c r="BC41" s="4" t="inlineStr"/>
@@ -10436,7 +10535,8 @@
       <c r="BG41" s="4" t="inlineStr"/>
       <c r="BH41" s="4" t="inlineStr"/>
       <c r="BI41" s="4" t="inlineStr"/>
-      <c r="BJ41" s="4" t="inlineStr">
+      <c r="BJ41" s="4" t="inlineStr"/>
+      <c r="BK41" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10592,25 +10692,25 @@
         </is>
       </c>
       <c r="AU42" s="4" t="inlineStr"/>
-      <c r="AV42" s="4" t="inlineStr">
+      <c r="AV42" s="4" t="inlineStr"/>
+      <c r="AW42" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW42" s="4" t="inlineStr">
+      <c r="AX42" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX42" s="4" t="inlineStr">
+      <c r="AY42" s="4" t="inlineStr">
         <is>
           <t>熊掌｜paw_bear</t>
         </is>
       </c>
-      <c r="AY42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ42" s="4" t="inlineStr"/>
+      <c r="AZ42" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA42" s="4" t="inlineStr"/>
       <c r="BB42" s="4" t="inlineStr"/>
       <c r="BC42" s="4" t="inlineStr"/>
@@ -10620,7 +10720,8 @@
       <c r="BG42" s="4" t="inlineStr"/>
       <c r="BH42" s="4" t="inlineStr"/>
       <c r="BI42" s="4" t="inlineStr"/>
-      <c r="BJ42" s="4" t="inlineStr">
+      <c r="BJ42" s="4" t="inlineStr"/>
+      <c r="BK42" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10776,25 +10877,25 @@
         </is>
       </c>
       <c r="AU43" s="4" t="inlineStr"/>
-      <c r="AV43" s="4" t="inlineStr">
+      <c r="AV43" s="4" t="inlineStr"/>
+      <c r="AW43" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW43" s="4" t="inlineStr">
+      <c r="AX43" s="4" t="inlineStr">
         <is>
           <t>right bottom</t>
         </is>
       </c>
-      <c r="AX43" s="4" t="inlineStr">
+      <c r="AY43" s="4" t="inlineStr">
         <is>
           <t>鹿角｜antler_deer</t>
         </is>
       </c>
-      <c r="AY43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ43" s="4" t="inlineStr"/>
+      <c r="AZ43" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA43" s="4" t="inlineStr"/>
       <c r="BB43" s="4" t="inlineStr"/>
       <c r="BC43" s="4" t="inlineStr"/>
@@ -10804,7 +10905,8 @@
       <c r="BG43" s="4" t="inlineStr"/>
       <c r="BH43" s="4" t="inlineStr"/>
       <c r="BI43" s="4" t="inlineStr"/>
-      <c r="BJ43" s="4" t="inlineStr">
+      <c r="BJ43" s="4" t="inlineStr"/>
+      <c r="BK43" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10960,25 +11062,25 @@
         </is>
       </c>
       <c r="AU44" s="4" t="inlineStr"/>
-      <c r="AV44" s="4" t="inlineStr">
+      <c r="AV44" s="4" t="inlineStr"/>
+      <c r="AW44" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW44" s="4" t="inlineStr">
+      <c r="AX44" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX44" s="4" t="inlineStr">
+      <c r="AY44" s="4" t="inlineStr">
         <is>
           <t>鹿角｜antler_deer</t>
         </is>
       </c>
-      <c r="AY44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ44" s="4" t="inlineStr"/>
+      <c r="AZ44" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA44" s="4" t="inlineStr"/>
       <c r="BB44" s="4" t="inlineStr"/>
       <c r="BC44" s="4" t="inlineStr"/>
@@ -10988,7 +11090,8 @@
       <c r="BG44" s="4" t="inlineStr"/>
       <c r="BH44" s="4" t="inlineStr"/>
       <c r="BI44" s="4" t="inlineStr"/>
-      <c r="BJ44" s="4" t="inlineStr">
+      <c r="BJ44" s="4" t="inlineStr"/>
+      <c r="BK44" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -11144,28 +11247,28 @@
         </is>
       </c>
       <c r="AU45" s="4" t="inlineStr"/>
-      <c r="AV45" s="4" t="inlineStr">
+      <c r="AV45" s="4" t="inlineStr"/>
+      <c r="AW45" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW45" s="4" t="inlineStr">
+      <c r="AX45" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX45" s="4" t="inlineStr">
+      <c r="AY45" s="4" t="inlineStr">
         <is>
           <t>禍魘之骨｜harm_bone</t>
         </is>
       </c>
-      <c r="AY45" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA45" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA45" s="4" t="inlineStr"/>
       <c r="BB45" s="4" t="inlineStr"/>
       <c r="BC45" s="4" t="inlineStr"/>
       <c r="BD45" s="4" t="inlineStr"/>
@@ -11174,7 +11277,8 @@
       <c r="BG45" s="4" t="inlineStr"/>
       <c r="BH45" s="4" t="inlineStr"/>
       <c r="BI45" s="4" t="inlineStr"/>
-      <c r="BJ45" s="4" t="inlineStr">
+      <c r="BJ45" s="4" t="inlineStr"/>
+      <c r="BK45" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -11332,28 +11436,28 @@
         </is>
       </c>
       <c r="AU46" s="4" t="inlineStr"/>
-      <c r="AV46" s="4" t="inlineStr">
+      <c r="AV46" s="4" t="inlineStr"/>
+      <c r="AW46" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW46" s="4" t="inlineStr">
+      <c r="AX46" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX46" s="4" t="inlineStr">
+      <c r="AY46" s="4" t="inlineStr">
         <is>
           <t>喪鐘碎片｜bell_shard</t>
         </is>
       </c>
-      <c r="AY46" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA46" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA46" s="4" t="inlineStr"/>
       <c r="BB46" s="4" t="inlineStr"/>
       <c r="BC46" s="4" t="inlineStr"/>
       <c r="BD46" s="4" t="inlineStr"/>
@@ -11362,7 +11466,8 @@
       <c r="BG46" s="4" t="inlineStr"/>
       <c r="BH46" s="4" t="inlineStr"/>
       <c r="BI46" s="4" t="inlineStr"/>
-      <c r="BJ46" s="4" t="inlineStr">
+      <c r="BJ46" s="4" t="inlineStr"/>
+      <c r="BK46" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -11518,17 +11623,17 @@
         </is>
       </c>
       <c r="AU47" s="4" t="inlineStr"/>
-      <c r="AV47" s="4" t="inlineStr">
+      <c r="AV47" s="4" t="inlineStr"/>
+      <c r="AW47" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW47" s="4" t="inlineStr">
+      <c r="AX47" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX47" s="4" t="inlineStr"/>
       <c r="AY47" s="4" t="inlineStr"/>
       <c r="AZ47" s="4" t="inlineStr"/>
       <c r="BA47" s="4" t="inlineStr"/>
@@ -11540,7 +11645,8 @@
       <c r="BG47" s="4" t="inlineStr"/>
       <c r="BH47" s="4" t="inlineStr"/>
       <c r="BI47" s="4" t="inlineStr"/>
-      <c r="BJ47" s="4" t="inlineStr">
+      <c r="BJ47" s="4" t="inlineStr"/>
+      <c r="BK47" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -11696,28 +11802,28 @@
         </is>
       </c>
       <c r="AU48" s="4" t="inlineStr"/>
-      <c r="AV48" s="4" t="inlineStr">
+      <c r="AV48" s="4" t="inlineStr"/>
+      <c r="AW48" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW48" s="4" t="inlineStr">
+      <c r="AX48" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX48" s="4" t="inlineStr">
+      <c r="AY48" s="4" t="inlineStr">
         <is>
           <t>禍魘之爪｜harm_claw</t>
         </is>
       </c>
-      <c r="AY48" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA48" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA48" s="4" t="inlineStr"/>
       <c r="BB48" s="4" t="inlineStr"/>
       <c r="BC48" s="4" t="inlineStr"/>
       <c r="BD48" s="4" t="inlineStr"/>
@@ -11726,7 +11832,8 @@
       <c r="BG48" s="4" t="inlineStr"/>
       <c r="BH48" s="4" t="inlineStr"/>
       <c r="BI48" s="4" t="inlineStr"/>
-      <c r="BJ48" s="4" t="inlineStr">
+      <c r="BJ48" s="4" t="inlineStr"/>
+      <c r="BK48" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -11884,28 +11991,28 @@
         </is>
       </c>
       <c r="AU49" s="4" t="inlineStr"/>
-      <c r="AV49" s="4" t="inlineStr">
+      <c r="AV49" s="4" t="inlineStr"/>
+      <c r="AW49" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW49" s="4" t="inlineStr">
+      <c r="AX49" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX49" s="4" t="inlineStr">
+      <c r="AY49" s="4" t="inlineStr">
         <is>
           <t>喪鐘碎片｜bell_shard</t>
         </is>
       </c>
-      <c r="AY49" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA49" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA49" s="4" t="inlineStr"/>
       <c r="BB49" s="4" t="inlineStr"/>
       <c r="BC49" s="4" t="inlineStr"/>
       <c r="BD49" s="4" t="inlineStr"/>
@@ -11914,7 +12021,8 @@
       <c r="BG49" s="4" t="inlineStr"/>
       <c r="BH49" s="4" t="inlineStr"/>
       <c r="BI49" s="4" t="inlineStr"/>
-      <c r="BJ49" s="4" t="inlineStr">
+      <c r="BJ49" s="4" t="inlineStr"/>
+      <c r="BK49" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -12070,25 +12178,25 @@
         </is>
       </c>
       <c r="AU50" s="4" t="inlineStr"/>
-      <c r="AV50" s="4" t="inlineStr">
+      <c r="AV50" s="4" t="inlineStr"/>
+      <c r="AW50" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW50" s="4" t="inlineStr">
+      <c r="AX50" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX50" s="4" t="inlineStr">
+      <c r="AY50" s="4" t="inlineStr">
         <is>
           <t>聖徒之爪｜saint_claw</t>
         </is>
       </c>
-      <c r="AY50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ50" s="4" t="inlineStr"/>
+      <c r="AZ50" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA50" s="4" t="inlineStr"/>
       <c r="BB50" s="4" t="inlineStr"/>
       <c r="BC50" s="4" t="inlineStr"/>
@@ -12098,7 +12206,8 @@
       <c r="BG50" s="4" t="inlineStr"/>
       <c r="BH50" s="4" t="inlineStr"/>
       <c r="BI50" s="4" t="inlineStr"/>
-      <c r="BJ50" s="4" t="inlineStr">
+      <c r="BJ50" s="4" t="inlineStr"/>
+      <c r="BK50" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -12254,25 +12363,25 @@
         </is>
       </c>
       <c r="AU51" s="4" t="inlineStr"/>
-      <c r="AV51" s="4" t="inlineStr">
+      <c r="AV51" s="4" t="inlineStr"/>
+      <c r="AW51" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW51" s="4" t="inlineStr">
+      <c r="AX51" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX51" s="4" t="inlineStr">
+      <c r="AY51" s="4" t="inlineStr">
         <is>
           <t>聖徒之牙｜saint_fang</t>
         </is>
       </c>
-      <c r="AY51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ51" s="4" t="inlineStr"/>
+      <c r="AZ51" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA51" s="4" t="inlineStr"/>
       <c r="BB51" s="4" t="inlineStr"/>
       <c r="BC51" s="4" t="inlineStr"/>
@@ -12282,7 +12391,8 @@
       <c r="BG51" s="4" t="inlineStr"/>
       <c r="BH51" s="4" t="inlineStr"/>
       <c r="BI51" s="4" t="inlineStr"/>
-      <c r="BJ51" s="4" t="inlineStr">
+      <c r="BJ51" s="4" t="inlineStr"/>
+      <c r="BK51" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -12440,25 +12550,25 @@
         </is>
       </c>
       <c r="AU52" s="4" t="inlineStr"/>
-      <c r="AV52" s="4" t="inlineStr">
+      <c r="AV52" s="4" t="inlineStr"/>
+      <c r="AW52" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW52" s="4" t="inlineStr">
+      <c r="AX52" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX52" s="4" t="inlineStr">
+      <c r="AY52" s="4" t="inlineStr">
         <is>
           <t>聖徒巨骨｜saint_bone_big</t>
         </is>
       </c>
-      <c r="AY52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ52" s="4" t="inlineStr"/>
+      <c r="AZ52" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA52" s="4" t="inlineStr"/>
       <c r="BB52" s="4" t="inlineStr"/>
       <c r="BC52" s="4" t="inlineStr"/>
@@ -12468,7 +12578,8 @@
       <c r="BG52" s="4" t="inlineStr"/>
       <c r="BH52" s="4" t="inlineStr"/>
       <c r="BI52" s="4" t="inlineStr"/>
-      <c r="BJ52" s="4" t="inlineStr">
+      <c r="BJ52" s="4" t="inlineStr"/>
+      <c r="BK52" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -12624,25 +12735,25 @@
         </is>
       </c>
       <c r="AU53" s="4" t="inlineStr"/>
-      <c r="AV53" s="4" t="inlineStr">
+      <c r="AV53" s="4" t="inlineStr"/>
+      <c r="AW53" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW53" s="4" t="inlineStr">
+      <c r="AX53" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX53" s="4" t="inlineStr">
+      <c r="AY53" s="4" t="inlineStr">
         <is>
           <t>聖徒之骨｜saint_bone</t>
         </is>
       </c>
-      <c r="AY53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ53" s="4" t="inlineStr"/>
+      <c r="AZ53" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BA53" s="4" t="inlineStr"/>
       <c r="BB53" s="4" t="inlineStr"/>
       <c r="BC53" s="4" t="inlineStr"/>
@@ -12652,7 +12763,8 @@
       <c r="BG53" s="4" t="inlineStr"/>
       <c r="BH53" s="4" t="inlineStr"/>
       <c r="BI53" s="4" t="inlineStr"/>
-      <c r="BJ53" s="4" t="inlineStr">
+      <c r="BJ53" s="4" t="inlineStr"/>
+      <c r="BK53" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -12814,17 +12926,17 @@
         </is>
       </c>
       <c r="AU54" s="4" t="inlineStr"/>
-      <c r="AV54" s="4" t="inlineStr">
+      <c r="AV54" s="4" t="inlineStr"/>
+      <c r="AW54" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW54" s="4" t="inlineStr">
+      <c r="AX54" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX54" s="4" t="inlineStr"/>
       <c r="AY54" s="4" t="inlineStr"/>
       <c r="AZ54" s="4" t="inlineStr"/>
       <c r="BA54" s="4" t="inlineStr"/>
@@ -12836,7 +12948,8 @@
       <c r="BG54" s="4" t="inlineStr"/>
       <c r="BH54" s="4" t="inlineStr"/>
       <c r="BI54" s="4" t="inlineStr"/>
-      <c r="BJ54" s="4" t="inlineStr">
+      <c r="BJ54" s="4" t="inlineStr"/>
+      <c r="BK54" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -12996,17 +13109,17 @@
         </is>
       </c>
       <c r="AU55" s="4" t="inlineStr"/>
-      <c r="AV55" s="4" t="inlineStr">
+      <c r="AV55" s="4" t="inlineStr"/>
+      <c r="AW55" s="4" t="inlineStr">
         <is>
           <t>cover</t>
         </is>
       </c>
-      <c r="AW55" s="4" t="inlineStr">
+      <c r="AX55" s="4" t="inlineStr">
         <is>
           <t>center top</t>
         </is>
       </c>
-      <c r="AX55" s="4" t="inlineStr"/>
       <c r="AY55" s="4" t="inlineStr"/>
       <c r="AZ55" s="4" t="inlineStr"/>
       <c r="BA55" s="4" t="inlineStr"/>
@@ -13018,7 +13131,8 @@
       <c r="BG55" s="4" t="inlineStr"/>
       <c r="BH55" s="4" t="inlineStr"/>
       <c r="BI55" s="4" t="inlineStr"/>
-      <c r="BJ55" s="4" t="inlineStr">
+      <c r="BJ55" s="4" t="inlineStr"/>
+      <c r="BK55" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -13178,17 +13292,17 @@
         </is>
       </c>
       <c r="AU56" s="4" t="inlineStr"/>
-      <c r="AV56" s="4" t="inlineStr">
+      <c r="AV56" s="4" t="inlineStr"/>
+      <c r="AW56" s="4" t="inlineStr">
         <is>
           <t>cover</t>
         </is>
       </c>
-      <c r="AW56" s="4" t="inlineStr">
+      <c r="AX56" s="4" t="inlineStr">
         <is>
           <t>center top</t>
         </is>
       </c>
-      <c r="AX56" s="4" t="inlineStr"/>
       <c r="AY56" s="4" t="inlineStr"/>
       <c r="AZ56" s="4" t="inlineStr"/>
       <c r="BA56" s="4" t="inlineStr"/>
@@ -13200,7 +13314,8 @@
       <c r="BG56" s="4" t="inlineStr"/>
       <c r="BH56" s="4" t="inlineStr"/>
       <c r="BI56" s="4" t="inlineStr"/>
-      <c r="BJ56" s="4" t="inlineStr">
+      <c r="BJ56" s="4" t="inlineStr"/>
+      <c r="BK56" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -13360,17 +13475,17 @@
         </is>
       </c>
       <c r="AU57" s="4" t="inlineStr"/>
-      <c r="AV57" s="4" t="inlineStr">
+      <c r="AV57" s="4" t="inlineStr"/>
+      <c r="AW57" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW57" s="4" t="inlineStr">
+      <c r="AX57" s="4" t="inlineStr">
         <is>
           <t>center 18%</t>
         </is>
       </c>
-      <c r="AX57" s="4" t="inlineStr"/>
       <c r="AY57" s="4" t="inlineStr"/>
       <c r="AZ57" s="4" t="inlineStr"/>
       <c r="BA57" s="4" t="inlineStr"/>
@@ -13382,7 +13497,8 @@
       <c r="BG57" s="4" t="inlineStr"/>
       <c r="BH57" s="4" t="inlineStr"/>
       <c r="BI57" s="4" t="inlineStr"/>
-      <c r="BJ57" s="4" t="inlineStr">
+      <c r="BJ57" s="4" t="inlineStr"/>
+      <c r="BK57" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -13542,17 +13658,19 @@
         </is>
       </c>
       <c r="AU58" s="4" t="inlineStr"/>
-      <c r="AV58" s="4" t="inlineStr">
+      <c r="AV58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW58" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW58" s="4" t="inlineStr">
+      <c r="AX58" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX58" s="4" t="inlineStr"/>
       <c r="AY58" s="4" t="inlineStr"/>
       <c r="AZ58" s="4" t="inlineStr"/>
       <c r="BA58" s="4" t="inlineStr"/>
@@ -13564,7 +13682,8 @@
       <c r="BG58" s="4" t="inlineStr"/>
       <c r="BH58" s="4" t="inlineStr"/>
       <c r="BI58" s="4" t="inlineStr"/>
-      <c r="BJ58" s="4" t="inlineStr">
+      <c r="BJ58" s="4" t="inlineStr"/>
+      <c r="BK58" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -13720,17 +13839,17 @@
         </is>
       </c>
       <c r="AU59" s="4" t="inlineStr"/>
-      <c r="AV59" s="4" t="inlineStr">
+      <c r="AV59" s="4" t="inlineStr"/>
+      <c r="AW59" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW59" s="4" t="inlineStr">
+      <c r="AX59" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX59" s="4" t="inlineStr"/>
       <c r="AY59" s="4" t="inlineStr"/>
       <c r="AZ59" s="4" t="inlineStr"/>
       <c r="BA59" s="4" t="inlineStr"/>
@@ -13742,7 +13861,8 @@
       <c r="BG59" s="4" t="inlineStr"/>
       <c r="BH59" s="4" t="inlineStr"/>
       <c r="BI59" s="4" t="inlineStr"/>
-      <c r="BJ59" s="4" t="inlineStr">
+      <c r="BJ59" s="4" t="inlineStr"/>
+      <c r="BK59" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -13898,17 +14018,17 @@
         </is>
       </c>
       <c r="AU60" s="4" t="inlineStr"/>
-      <c r="AV60" s="4" t="inlineStr">
+      <c r="AV60" s="4" t="inlineStr"/>
+      <c r="AW60" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW60" s="4" t="inlineStr">
+      <c r="AX60" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX60" s="4" t="inlineStr"/>
       <c r="AY60" s="4" t="inlineStr"/>
       <c r="AZ60" s="4" t="inlineStr"/>
       <c r="BA60" s="4" t="inlineStr"/>
@@ -13920,7 +14040,8 @@
       <c r="BG60" s="4" t="inlineStr"/>
       <c r="BH60" s="4" t="inlineStr"/>
       <c r="BI60" s="4" t="inlineStr"/>
-      <c r="BJ60" s="4" t="inlineStr">
+      <c r="BJ60" s="4" t="inlineStr"/>
+      <c r="BK60" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -14076,17 +14197,17 @@
         </is>
       </c>
       <c r="AU61" s="4" t="inlineStr"/>
-      <c r="AV61" s="4" t="inlineStr">
+      <c r="AV61" s="4" t="inlineStr"/>
+      <c r="AW61" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW61" s="4" t="inlineStr">
+      <c r="AX61" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX61" s="4" t="inlineStr"/>
       <c r="AY61" s="4" t="inlineStr"/>
       <c r="AZ61" s="4" t="inlineStr"/>
       <c r="BA61" s="4" t="inlineStr"/>
@@ -14098,7 +14219,8 @@
       <c r="BG61" s="4" t="inlineStr"/>
       <c r="BH61" s="4" t="inlineStr"/>
       <c r="BI61" s="4" t="inlineStr"/>
-      <c r="BJ61" s="4" t="inlineStr">
+      <c r="BJ61" s="4" t="inlineStr"/>
+      <c r="BK61" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -14254,17 +14376,17 @@
         </is>
       </c>
       <c r="AU62" s="4" t="inlineStr"/>
-      <c r="AV62" s="4" t="inlineStr">
+      <c r="AV62" s="4" t="inlineStr"/>
+      <c r="AW62" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW62" s="4" t="inlineStr">
+      <c r="AX62" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX62" s="4" t="inlineStr"/>
       <c r="AY62" s="4" t="inlineStr"/>
       <c r="AZ62" s="4" t="inlineStr"/>
       <c r="BA62" s="4" t="inlineStr"/>
@@ -14276,7 +14398,8 @@
       <c r="BG62" s="4" t="inlineStr"/>
       <c r="BH62" s="4" t="inlineStr"/>
       <c r="BI62" s="4" t="inlineStr"/>
-      <c r="BJ62" s="4" t="inlineStr">
+      <c r="BJ62" s="4" t="inlineStr"/>
+      <c r="BK62" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -14432,17 +14555,17 @@
         </is>
       </c>
       <c r="AU63" s="4" t="inlineStr"/>
-      <c r="AV63" s="4" t="inlineStr">
+      <c r="AV63" s="4" t="inlineStr"/>
+      <c r="AW63" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW63" s="4" t="inlineStr">
+      <c r="AX63" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX63" s="4" t="inlineStr"/>
       <c r="AY63" s="4" t="inlineStr"/>
       <c r="AZ63" s="4" t="inlineStr"/>
       <c r="BA63" s="4" t="inlineStr"/>
@@ -14454,7 +14577,8 @@
       <c r="BG63" s="4" t="inlineStr"/>
       <c r="BH63" s="4" t="inlineStr"/>
       <c r="BI63" s="4" t="inlineStr"/>
-      <c r="BJ63" s="4" t="inlineStr">
+      <c r="BJ63" s="4" t="inlineStr"/>
+      <c r="BK63" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -14604,17 +14728,17 @@
         </is>
       </c>
       <c r="AU64" s="4" t="inlineStr"/>
-      <c r="AV64" s="4" t="inlineStr">
+      <c r="AV64" s="4" t="inlineStr"/>
+      <c r="AW64" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW64" s="4" t="inlineStr">
+      <c r="AX64" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX64" s="4" t="inlineStr"/>
       <c r="AY64" s="4" t="inlineStr"/>
       <c r="AZ64" s="4" t="inlineStr"/>
       <c r="BA64" s="4" t="inlineStr"/>
@@ -14626,7 +14750,8 @@
       <c r="BG64" s="4" t="inlineStr"/>
       <c r="BH64" s="4" t="inlineStr"/>
       <c r="BI64" s="4" t="inlineStr"/>
-      <c r="BJ64" s="4" t="inlineStr">
+      <c r="BJ64" s="4" t="inlineStr"/>
+      <c r="BK64" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -14782,17 +14907,17 @@
         </is>
       </c>
       <c r="AU65" s="4" t="inlineStr"/>
-      <c r="AV65" s="4" t="inlineStr">
+      <c r="AV65" s="4" t="inlineStr"/>
+      <c r="AW65" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW65" s="4" t="inlineStr">
+      <c r="AX65" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX65" s="4" t="inlineStr"/>
       <c r="AY65" s="4" t="inlineStr"/>
       <c r="AZ65" s="4" t="inlineStr"/>
       <c r="BA65" s="4" t="inlineStr"/>
@@ -14804,7 +14929,8 @@
       <c r="BG65" s="4" t="inlineStr"/>
       <c r="BH65" s="4" t="inlineStr"/>
       <c r="BI65" s="4" t="inlineStr"/>
-      <c r="BJ65" s="4" t="inlineStr">
+      <c r="BJ65" s="4" t="inlineStr"/>
+      <c r="BK65" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -14960,17 +15086,17 @@
         </is>
       </c>
       <c r="AU66" s="4" t="inlineStr"/>
-      <c r="AV66" s="4" t="inlineStr">
+      <c r="AV66" s="4" t="inlineStr"/>
+      <c r="AW66" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW66" s="4" t="inlineStr">
+      <c r="AX66" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX66" s="4" t="inlineStr"/>
       <c r="AY66" s="4" t="inlineStr"/>
       <c r="AZ66" s="4" t="inlineStr"/>
       <c r="BA66" s="4" t="inlineStr"/>
@@ -14982,7 +15108,8 @@
       <c r="BG66" s="4" t="inlineStr"/>
       <c r="BH66" s="4" t="inlineStr"/>
       <c r="BI66" s="4" t="inlineStr"/>
-      <c r="BJ66" s="4" t="inlineStr">
+      <c r="BJ66" s="4" t="inlineStr"/>
+      <c r="BK66" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -15138,17 +15265,17 @@
         </is>
       </c>
       <c r="AU67" s="4" t="inlineStr"/>
-      <c r="AV67" s="4" t="inlineStr">
+      <c r="AV67" s="4" t="inlineStr"/>
+      <c r="AW67" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW67" s="4" t="inlineStr">
+      <c r="AX67" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX67" s="4" t="inlineStr"/>
       <c r="AY67" s="4" t="inlineStr"/>
       <c r="AZ67" s="4" t="inlineStr"/>
       <c r="BA67" s="4" t="inlineStr"/>
@@ -15160,7 +15287,8 @@
       <c r="BG67" s="4" t="inlineStr"/>
       <c r="BH67" s="4" t="inlineStr"/>
       <c r="BI67" s="4" t="inlineStr"/>
-      <c r="BJ67" s="4" t="inlineStr">
+      <c r="BJ67" s="4" t="inlineStr"/>
+      <c r="BK67" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -15316,17 +15444,17 @@
         </is>
       </c>
       <c r="AU68" s="4" t="inlineStr"/>
-      <c r="AV68" s="4" t="inlineStr">
+      <c r="AV68" s="4" t="inlineStr"/>
+      <c r="AW68" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW68" s="4" t="inlineStr">
+      <c r="AX68" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX68" s="4" t="inlineStr"/>
       <c r="AY68" s="4" t="inlineStr"/>
       <c r="AZ68" s="4" t="inlineStr"/>
       <c r="BA68" s="4" t="inlineStr"/>
@@ -15338,7 +15466,8 @@
       <c r="BG68" s="4" t="inlineStr"/>
       <c r="BH68" s="4" t="inlineStr"/>
       <c r="BI68" s="4" t="inlineStr"/>
-      <c r="BJ68" s="4" t="inlineStr">
+      <c r="BJ68" s="4" t="inlineStr"/>
+      <c r="BK68" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -15490,17 +15619,17 @@
         </is>
       </c>
       <c r="AU69" s="4" t="inlineStr"/>
-      <c r="AV69" s="4" t="inlineStr">
+      <c r="AV69" s="4" t="inlineStr"/>
+      <c r="AW69" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW69" s="4" t="inlineStr">
+      <c r="AX69" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX69" s="4" t="inlineStr"/>
       <c r="AY69" s="4" t="inlineStr"/>
       <c r="AZ69" s="4" t="inlineStr"/>
       <c r="BA69" s="4" t="inlineStr"/>
@@ -15512,7 +15641,8 @@
       <c r="BG69" s="4" t="inlineStr"/>
       <c r="BH69" s="4" t="inlineStr"/>
       <c r="BI69" s="4" t="inlineStr"/>
-      <c r="BJ69" s="4" t="inlineStr">
+      <c r="BJ69" s="4" t="inlineStr"/>
+      <c r="BK69" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -15664,17 +15794,17 @@
         </is>
       </c>
       <c r="AU70" s="4" t="inlineStr"/>
-      <c r="AV70" s="4" t="inlineStr">
+      <c r="AV70" s="4" t="inlineStr"/>
+      <c r="AW70" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW70" s="4" t="inlineStr">
+      <c r="AX70" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX70" s="4" t="inlineStr"/>
       <c r="AY70" s="4" t="inlineStr"/>
       <c r="AZ70" s="4" t="inlineStr"/>
       <c r="BA70" s="4" t="inlineStr"/>
@@ -15686,7 +15816,8 @@
       <c r="BG70" s="4" t="inlineStr"/>
       <c r="BH70" s="4" t="inlineStr"/>
       <c r="BI70" s="4" t="inlineStr"/>
-      <c r="BJ70" s="4" t="inlineStr">
+      <c r="BJ70" s="4" t="inlineStr"/>
+      <c r="BK70" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -15840,17 +15971,17 @@
         </is>
       </c>
       <c r="AU71" s="4" t="inlineStr"/>
-      <c r="AV71" s="4" t="inlineStr">
+      <c r="AV71" s="4" t="inlineStr"/>
+      <c r="AW71" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW71" s="4" t="inlineStr">
+      <c r="AX71" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX71" s="4" t="inlineStr"/>
       <c r="AY71" s="4" t="inlineStr"/>
       <c r="AZ71" s="4" t="inlineStr"/>
       <c r="BA71" s="4" t="inlineStr"/>
@@ -15862,7 +15993,8 @@
       <c r="BG71" s="4" t="inlineStr"/>
       <c r="BH71" s="4" t="inlineStr"/>
       <c r="BI71" s="4" t="inlineStr"/>
-      <c r="BJ71" s="4" t="inlineStr">
+      <c r="BJ71" s="4" t="inlineStr"/>
+      <c r="BK71" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -16024,17 +16156,17 @@
         </is>
       </c>
       <c r="AU72" s="4" t="inlineStr"/>
-      <c r="AV72" s="4" t="inlineStr">
+      <c r="AV72" s="4" t="inlineStr"/>
+      <c r="AW72" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW72" s="4" t="inlineStr">
+      <c r="AX72" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX72" s="4" t="inlineStr"/>
       <c r="AY72" s="4" t="inlineStr"/>
       <c r="AZ72" s="4" t="inlineStr"/>
       <c r="BA72" s="4" t="inlineStr"/>
@@ -16046,7 +16178,8 @@
       <c r="BG72" s="4" t="inlineStr"/>
       <c r="BH72" s="4" t="inlineStr"/>
       <c r="BI72" s="4" t="inlineStr"/>
-      <c r="BJ72" s="4" t="inlineStr">
+      <c r="BJ72" s="4" t="inlineStr"/>
+      <c r="BK72" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -16208,17 +16341,17 @@
         </is>
       </c>
       <c r="AU73" s="4" t="inlineStr"/>
-      <c r="AV73" s="4" t="inlineStr">
+      <c r="AV73" s="4" t="inlineStr"/>
+      <c r="AW73" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW73" s="4" t="inlineStr">
+      <c r="AX73" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX73" s="4" t="inlineStr"/>
       <c r="AY73" s="4" t="inlineStr"/>
       <c r="AZ73" s="4" t="inlineStr"/>
       <c r="BA73" s="4" t="inlineStr"/>
@@ -16230,7 +16363,8 @@
       <c r="BG73" s="4" t="inlineStr"/>
       <c r="BH73" s="4" t="inlineStr"/>
       <c r="BI73" s="4" t="inlineStr"/>
-      <c r="BJ73" s="4" t="inlineStr">
+      <c r="BJ73" s="4" t="inlineStr"/>
+      <c r="BK73" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -16392,17 +16526,17 @@
         </is>
       </c>
       <c r="AU74" s="4" t="inlineStr"/>
-      <c r="AV74" s="4" t="inlineStr">
+      <c r="AV74" s="4" t="inlineStr"/>
+      <c r="AW74" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW74" s="4" t="inlineStr">
+      <c r="AX74" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX74" s="4" t="inlineStr"/>
       <c r="AY74" s="4" t="inlineStr"/>
       <c r="AZ74" s="4" t="inlineStr"/>
       <c r="BA74" s="4" t="inlineStr"/>
@@ -16414,7 +16548,8 @@
       <c r="BG74" s="4" t="inlineStr"/>
       <c r="BH74" s="4" t="inlineStr"/>
       <c r="BI74" s="4" t="inlineStr"/>
-      <c r="BJ74" s="4" t="inlineStr">
+      <c r="BJ74" s="4" t="inlineStr"/>
+      <c r="BK74" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -16576,17 +16711,17 @@
         </is>
       </c>
       <c r="AU75" s="4" t="inlineStr"/>
-      <c r="AV75" s="4" t="inlineStr">
+      <c r="AV75" s="4" t="inlineStr"/>
+      <c r="AW75" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW75" s="4" t="inlineStr">
+      <c r="AX75" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX75" s="4" t="inlineStr"/>
       <c r="AY75" s="4" t="inlineStr"/>
       <c r="AZ75" s="4" t="inlineStr"/>
       <c r="BA75" s="4" t="inlineStr"/>
@@ -16598,7 +16733,8 @@
       <c r="BG75" s="4" t="inlineStr"/>
       <c r="BH75" s="4" t="inlineStr"/>
       <c r="BI75" s="4" t="inlineStr"/>
-      <c r="BJ75" s="4" t="inlineStr">
+      <c r="BJ75" s="4" t="inlineStr"/>
+      <c r="BK75" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -16758,17 +16894,17 @@
         </is>
       </c>
       <c r="AU76" s="4" t="inlineStr"/>
-      <c r="AV76" s="4" t="inlineStr">
+      <c r="AV76" s="4" t="inlineStr"/>
+      <c r="AW76" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW76" s="4" t="inlineStr">
+      <c r="AX76" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX76" s="4" t="inlineStr"/>
       <c r="AY76" s="4" t="inlineStr"/>
       <c r="AZ76" s="4" t="inlineStr"/>
       <c r="BA76" s="4" t="inlineStr"/>
@@ -16780,7 +16916,8 @@
       <c r="BG76" s="4" t="inlineStr"/>
       <c r="BH76" s="4" t="inlineStr"/>
       <c r="BI76" s="4" t="inlineStr"/>
-      <c r="BJ76" s="4" t="inlineStr">
+      <c r="BJ76" s="4" t="inlineStr"/>
+      <c r="BK76" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -16940,17 +17077,17 @@
         </is>
       </c>
       <c r="AU77" s="4" t="inlineStr"/>
-      <c r="AV77" s="4" t="inlineStr">
+      <c r="AV77" s="4" t="inlineStr"/>
+      <c r="AW77" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW77" s="4" t="inlineStr">
+      <c r="AX77" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX77" s="4" t="inlineStr"/>
       <c r="AY77" s="4" t="inlineStr"/>
       <c r="AZ77" s="4" t="inlineStr"/>
       <c r="BA77" s="4" t="inlineStr"/>
@@ -16962,7 +17099,8 @@
       <c r="BG77" s="4" t="inlineStr"/>
       <c r="BH77" s="4" t="inlineStr"/>
       <c r="BI77" s="4" t="inlineStr"/>
-      <c r="BJ77" s="4" t="inlineStr">
+      <c r="BJ77" s="4" t="inlineStr"/>
+      <c r="BK77" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -17122,17 +17260,17 @@
         </is>
       </c>
       <c r="AU78" s="4" t="inlineStr"/>
-      <c r="AV78" s="4" t="inlineStr">
+      <c r="AV78" s="4" t="inlineStr"/>
+      <c r="AW78" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW78" s="4" t="inlineStr">
+      <c r="AX78" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX78" s="4" t="inlineStr"/>
       <c r="AY78" s="4" t="inlineStr"/>
       <c r="AZ78" s="4" t="inlineStr"/>
       <c r="BA78" s="4" t="inlineStr"/>
@@ -17144,7 +17282,8 @@
       <c r="BG78" s="4" t="inlineStr"/>
       <c r="BH78" s="4" t="inlineStr"/>
       <c r="BI78" s="4" t="inlineStr"/>
-      <c r="BJ78" s="4" t="inlineStr">
+      <c r="BJ78" s="4" t="inlineStr"/>
+      <c r="BK78" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -17304,17 +17443,17 @@
         </is>
       </c>
       <c r="AU79" s="4" t="inlineStr"/>
-      <c r="AV79" s="4" t="inlineStr">
+      <c r="AV79" s="4" t="inlineStr"/>
+      <c r="AW79" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW79" s="4" t="inlineStr">
+      <c r="AX79" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX79" s="4" t="inlineStr"/>
       <c r="AY79" s="4" t="inlineStr"/>
       <c r="AZ79" s="4" t="inlineStr"/>
       <c r="BA79" s="4" t="inlineStr"/>
@@ -17326,7 +17465,8 @@
       <c r="BG79" s="4" t="inlineStr"/>
       <c r="BH79" s="4" t="inlineStr"/>
       <c r="BI79" s="4" t="inlineStr"/>
-      <c r="BJ79" s="4" t="inlineStr">
+      <c r="BJ79" s="4" t="inlineStr"/>
+      <c r="BK79" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -17488,17 +17628,17 @@
         </is>
       </c>
       <c r="AU80" s="4" t="inlineStr"/>
-      <c r="AV80" s="4" t="inlineStr">
+      <c r="AV80" s="4" t="inlineStr"/>
+      <c r="AW80" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW80" s="4" t="inlineStr">
+      <c r="AX80" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX80" s="4" t="inlineStr"/>
       <c r="AY80" s="4" t="inlineStr"/>
       <c r="AZ80" s="4" t="inlineStr"/>
       <c r="BA80" s="4" t="inlineStr"/>
@@ -17510,7 +17650,8 @@
       <c r="BG80" s="4" t="inlineStr"/>
       <c r="BH80" s="4" t="inlineStr"/>
       <c r="BI80" s="4" t="inlineStr"/>
-      <c r="BJ80" s="4" t="inlineStr">
+      <c r="BJ80" s="4" t="inlineStr"/>
+      <c r="BK80" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -17670,17 +17811,17 @@
         </is>
       </c>
       <c r="AU81" s="4" t="inlineStr"/>
-      <c r="AV81" s="4" t="inlineStr">
+      <c r="AV81" s="4" t="inlineStr"/>
+      <c r="AW81" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW81" s="4" t="inlineStr">
+      <c r="AX81" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX81" s="4" t="inlineStr"/>
       <c r="AY81" s="4" t="inlineStr"/>
       <c r="AZ81" s="4" t="inlineStr"/>
       <c r="BA81" s="4" t="inlineStr"/>
@@ -17692,7 +17833,8 @@
       <c r="BG81" s="4" t="inlineStr"/>
       <c r="BH81" s="4" t="inlineStr"/>
       <c r="BI81" s="4" t="inlineStr"/>
-      <c r="BJ81" s="4" t="inlineStr">
+      <c r="BJ81" s="4" t="inlineStr"/>
+      <c r="BK81" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -17852,17 +17994,17 @@
         </is>
       </c>
       <c r="AU82" s="4" t="inlineStr"/>
-      <c r="AV82" s="4" t="inlineStr">
+      <c r="AV82" s="4" t="inlineStr"/>
+      <c r="AW82" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW82" s="4" t="inlineStr">
+      <c r="AX82" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX82" s="4" t="inlineStr"/>
       <c r="AY82" s="4" t="inlineStr"/>
       <c r="AZ82" s="4" t="inlineStr"/>
       <c r="BA82" s="4" t="inlineStr"/>
@@ -17874,7 +18016,8 @@
       <c r="BG82" s="4" t="inlineStr"/>
       <c r="BH82" s="4" t="inlineStr"/>
       <c r="BI82" s="4" t="inlineStr"/>
-      <c r="BJ82" s="4" t="inlineStr">
+      <c r="BJ82" s="4" t="inlineStr"/>
+      <c r="BK82" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -18034,17 +18177,17 @@
         </is>
       </c>
       <c r="AU83" s="4" t="inlineStr"/>
-      <c r="AV83" s="4" t="inlineStr">
+      <c r="AV83" s="4" t="inlineStr"/>
+      <c r="AW83" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW83" s="4" t="inlineStr">
+      <c r="AX83" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX83" s="4" t="inlineStr"/>
       <c r="AY83" s="4" t="inlineStr"/>
       <c r="AZ83" s="4" t="inlineStr"/>
       <c r="BA83" s="4" t="inlineStr"/>
@@ -18056,7 +18199,8 @@
       <c r="BG83" s="4" t="inlineStr"/>
       <c r="BH83" s="4" t="inlineStr"/>
       <c r="BI83" s="4" t="inlineStr"/>
-      <c r="BJ83" s="4" t="inlineStr">
+      <c r="BJ83" s="4" t="inlineStr"/>
+      <c r="BK83" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -18216,17 +18360,17 @@
         </is>
       </c>
       <c r="AU84" s="4" t="inlineStr"/>
-      <c r="AV84" s="4" t="inlineStr">
+      <c r="AV84" s="4" t="inlineStr"/>
+      <c r="AW84" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW84" s="4" t="inlineStr">
+      <c r="AX84" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX84" s="4" t="inlineStr"/>
       <c r="AY84" s="4" t="inlineStr"/>
       <c r="AZ84" s="4" t="inlineStr"/>
       <c r="BA84" s="4" t="inlineStr"/>
@@ -18238,7 +18382,8 @@
       <c r="BG84" s="4" t="inlineStr"/>
       <c r="BH84" s="4" t="inlineStr"/>
       <c r="BI84" s="4" t="inlineStr"/>
-      <c r="BJ84" s="4" t="inlineStr">
+      <c r="BJ84" s="4" t="inlineStr"/>
+      <c r="BK84" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -18398,17 +18543,17 @@
         </is>
       </c>
       <c r="AU85" s="4" t="inlineStr"/>
-      <c r="AV85" s="4" t="inlineStr">
+      <c r="AV85" s="4" t="inlineStr"/>
+      <c r="AW85" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW85" s="4" t="inlineStr">
+      <c r="AX85" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX85" s="4" t="inlineStr"/>
       <c r="AY85" s="4" t="inlineStr"/>
       <c r="AZ85" s="4" t="inlineStr"/>
       <c r="BA85" s="4" t="inlineStr"/>
@@ -18420,7 +18565,8 @@
       <c r="BG85" s="4" t="inlineStr"/>
       <c r="BH85" s="4" t="inlineStr"/>
       <c r="BI85" s="4" t="inlineStr"/>
-      <c r="BJ85" s="4" t="inlineStr">
+      <c r="BJ85" s="4" t="inlineStr"/>
+      <c r="BK85" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -18580,17 +18726,17 @@
         </is>
       </c>
       <c r="AU86" s="4" t="inlineStr"/>
-      <c r="AV86" s="4" t="inlineStr">
+      <c r="AV86" s="4" t="inlineStr"/>
+      <c r="AW86" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW86" s="4" t="inlineStr">
+      <c r="AX86" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX86" s="4" t="inlineStr"/>
       <c r="AY86" s="4" t="inlineStr"/>
       <c r="AZ86" s="4" t="inlineStr"/>
       <c r="BA86" s="4" t="inlineStr"/>
@@ -18602,7 +18748,8 @@
       <c r="BG86" s="4" t="inlineStr"/>
       <c r="BH86" s="4" t="inlineStr"/>
       <c r="BI86" s="4" t="inlineStr"/>
-      <c r="BJ86" s="4" t="inlineStr">
+      <c r="BJ86" s="4" t="inlineStr"/>
+      <c r="BK86" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -18762,17 +18909,17 @@
         </is>
       </c>
       <c r="AU87" s="4" t="inlineStr"/>
-      <c r="AV87" s="4" t="inlineStr">
+      <c r="AV87" s="4" t="inlineStr"/>
+      <c r="AW87" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW87" s="4" t="inlineStr">
+      <c r="AX87" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX87" s="4" t="inlineStr"/>
       <c r="AY87" s="4" t="inlineStr"/>
       <c r="AZ87" s="4" t="inlineStr"/>
       <c r="BA87" s="4" t="inlineStr"/>
@@ -18784,7 +18931,8 @@
       <c r="BG87" s="4" t="inlineStr"/>
       <c r="BH87" s="4" t="inlineStr"/>
       <c r="BI87" s="4" t="inlineStr"/>
-      <c r="BJ87" s="4" t="inlineStr">
+      <c r="BJ87" s="4" t="inlineStr"/>
+      <c r="BK87" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -18946,17 +19094,17 @@
         </is>
       </c>
       <c r="AU88" s="4" t="inlineStr"/>
-      <c r="AV88" s="4" t="inlineStr">
+      <c r="AV88" s="4" t="inlineStr"/>
+      <c r="AW88" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW88" s="4" t="inlineStr">
+      <c r="AX88" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX88" s="4" t="inlineStr"/>
       <c r="AY88" s="4" t="inlineStr"/>
       <c r="AZ88" s="4" t="inlineStr"/>
       <c r="BA88" s="4" t="inlineStr"/>
@@ -18968,7 +19116,8 @@
       <c r="BG88" s="4" t="inlineStr"/>
       <c r="BH88" s="4" t="inlineStr"/>
       <c r="BI88" s="4" t="inlineStr"/>
-      <c r="BJ88" s="4" t="inlineStr">
+      <c r="BJ88" s="4" t="inlineStr"/>
+      <c r="BK88" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -19128,17 +19277,17 @@
         </is>
       </c>
       <c r="AU89" s="4" t="inlineStr"/>
-      <c r="AV89" s="4" t="inlineStr">
+      <c r="AV89" s="4" t="inlineStr"/>
+      <c r="AW89" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW89" s="4" t="inlineStr">
+      <c r="AX89" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX89" s="4" t="inlineStr"/>
       <c r="AY89" s="4" t="inlineStr"/>
       <c r="AZ89" s="4" t="inlineStr"/>
       <c r="BA89" s="4" t="inlineStr"/>
@@ -19150,7 +19299,8 @@
       <c r="BG89" s="4" t="inlineStr"/>
       <c r="BH89" s="4" t="inlineStr"/>
       <c r="BI89" s="4" t="inlineStr"/>
-      <c r="BJ89" s="4" t="inlineStr">
+      <c r="BJ89" s="4" t="inlineStr"/>
+      <c r="BK89" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -19310,17 +19460,17 @@
         </is>
       </c>
       <c r="AU90" s="4" t="inlineStr"/>
-      <c r="AV90" s="4" t="inlineStr">
+      <c r="AV90" s="4" t="inlineStr"/>
+      <c r="AW90" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW90" s="4" t="inlineStr">
+      <c r="AX90" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX90" s="4" t="inlineStr"/>
       <c r="AY90" s="4" t="inlineStr"/>
       <c r="AZ90" s="4" t="inlineStr"/>
       <c r="BA90" s="4" t="inlineStr"/>
@@ -19332,7 +19482,8 @@
       <c r="BG90" s="4" t="inlineStr"/>
       <c r="BH90" s="4" t="inlineStr"/>
       <c r="BI90" s="4" t="inlineStr"/>
-      <c r="BJ90" s="4" t="inlineStr">
+      <c r="BJ90" s="4" t="inlineStr"/>
+      <c r="BK90" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -19492,17 +19643,17 @@
         </is>
       </c>
       <c r="AU91" s="4" t="inlineStr"/>
-      <c r="AV91" s="4" t="inlineStr">
+      <c r="AV91" s="4" t="inlineStr"/>
+      <c r="AW91" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW91" s="4" t="inlineStr">
+      <c r="AX91" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX91" s="4" t="inlineStr"/>
       <c r="AY91" s="4" t="inlineStr"/>
       <c r="AZ91" s="4" t="inlineStr"/>
       <c r="BA91" s="4" t="inlineStr"/>
@@ -19514,7 +19665,8 @@
       <c r="BG91" s="4" t="inlineStr"/>
       <c r="BH91" s="4" t="inlineStr"/>
       <c r="BI91" s="4" t="inlineStr"/>
-      <c r="BJ91" s="4" t="inlineStr">
+      <c r="BJ91" s="4" t="inlineStr"/>
+      <c r="BK91" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -19674,17 +19826,17 @@
         </is>
       </c>
       <c r="AU92" s="4" t="inlineStr"/>
-      <c r="AV92" s="4" t="inlineStr">
+      <c r="AV92" s="4" t="inlineStr"/>
+      <c r="AW92" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW92" s="4" t="inlineStr">
+      <c r="AX92" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX92" s="4" t="inlineStr"/>
       <c r="AY92" s="4" t="inlineStr"/>
       <c r="AZ92" s="4" t="inlineStr"/>
       <c r="BA92" s="4" t="inlineStr"/>
@@ -19696,7 +19848,8 @@
       <c r="BG92" s="4" t="inlineStr"/>
       <c r="BH92" s="4" t="inlineStr"/>
       <c r="BI92" s="4" t="inlineStr"/>
-      <c r="BJ92" s="4" t="inlineStr">
+      <c r="BJ92" s="4" t="inlineStr"/>
+      <c r="BK92" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -19858,17 +20011,17 @@
         </is>
       </c>
       <c r="AU93" s="4" t="inlineStr"/>
-      <c r="AV93" s="4" t="inlineStr">
+      <c r="AV93" s="4" t="inlineStr"/>
+      <c r="AW93" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW93" s="4" t="inlineStr">
+      <c r="AX93" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX93" s="4" t="inlineStr"/>
       <c r="AY93" s="4" t="inlineStr"/>
       <c r="AZ93" s="4" t="inlineStr"/>
       <c r="BA93" s="4" t="inlineStr"/>
@@ -19880,7 +20033,8 @@
       <c r="BG93" s="4" t="inlineStr"/>
       <c r="BH93" s="4" t="inlineStr"/>
       <c r="BI93" s="4" t="inlineStr"/>
-      <c r="BJ93" s="4" t="inlineStr">
+      <c r="BJ93" s="4" t="inlineStr"/>
+      <c r="BK93" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -20040,17 +20194,17 @@
         </is>
       </c>
       <c r="AU94" s="4" t="inlineStr"/>
-      <c r="AV94" s="4" t="inlineStr">
+      <c r="AV94" s="4" t="inlineStr"/>
+      <c r="AW94" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW94" s="4" t="inlineStr">
+      <c r="AX94" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX94" s="4" t="inlineStr"/>
       <c r="AY94" s="4" t="inlineStr"/>
       <c r="AZ94" s="4" t="inlineStr"/>
       <c r="BA94" s="4" t="inlineStr"/>
@@ -20062,7 +20216,8 @@
       <c r="BG94" s="4" t="inlineStr"/>
       <c r="BH94" s="4" t="inlineStr"/>
       <c r="BI94" s="4" t="inlineStr"/>
-      <c r="BJ94" s="4" t="inlineStr">
+      <c r="BJ94" s="4" t="inlineStr"/>
+      <c r="BK94" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -20222,17 +20377,17 @@
         </is>
       </c>
       <c r="AU95" s="4" t="inlineStr"/>
-      <c r="AV95" s="4" t="inlineStr">
+      <c r="AV95" s="4" t="inlineStr"/>
+      <c r="AW95" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW95" s="4" t="inlineStr">
+      <c r="AX95" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX95" s="4" t="inlineStr"/>
       <c r="AY95" s="4" t="inlineStr"/>
       <c r="AZ95" s="4" t="inlineStr"/>
       <c r="BA95" s="4" t="inlineStr"/>
@@ -20244,7 +20399,8 @@
       <c r="BG95" s="4" t="inlineStr"/>
       <c r="BH95" s="4" t="inlineStr"/>
       <c r="BI95" s="4" t="inlineStr"/>
-      <c r="BJ95" s="4" t="inlineStr">
+      <c r="BJ95" s="4" t="inlineStr"/>
+      <c r="BK95" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -20404,17 +20560,17 @@
         </is>
       </c>
       <c r="AU96" s="4" t="inlineStr"/>
-      <c r="AV96" s="4" t="inlineStr">
+      <c r="AV96" s="4" t="inlineStr"/>
+      <c r="AW96" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW96" s="4" t="inlineStr">
+      <c r="AX96" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX96" s="4" t="inlineStr"/>
       <c r="AY96" s="4" t="inlineStr"/>
       <c r="AZ96" s="4" t="inlineStr"/>
       <c r="BA96" s="4" t="inlineStr"/>
@@ -20426,7 +20582,8 @@
       <c r="BG96" s="4" t="inlineStr"/>
       <c r="BH96" s="4" t="inlineStr"/>
       <c r="BI96" s="4" t="inlineStr"/>
-      <c r="BJ96" s="4" t="inlineStr">
+      <c r="BJ96" s="4" t="inlineStr"/>
+      <c r="BK96" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -20586,17 +20743,17 @@
         </is>
       </c>
       <c r="AU97" s="4" t="inlineStr"/>
-      <c r="AV97" s="4" t="inlineStr">
+      <c r="AV97" s="4" t="inlineStr"/>
+      <c r="AW97" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW97" s="4" t="inlineStr">
+      <c r="AX97" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX97" s="4" t="inlineStr"/>
       <c r="AY97" s="4" t="inlineStr"/>
       <c r="AZ97" s="4" t="inlineStr"/>
       <c r="BA97" s="4" t="inlineStr"/>
@@ -20608,7 +20765,8 @@
       <c r="BG97" s="4" t="inlineStr"/>
       <c r="BH97" s="4" t="inlineStr"/>
       <c r="BI97" s="4" t="inlineStr"/>
-      <c r="BJ97" s="4" t="inlineStr">
+      <c r="BJ97" s="4" t="inlineStr"/>
+      <c r="BK97" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -20764,17 +20922,17 @@
         </is>
       </c>
       <c r="AU98" s="4" t="inlineStr"/>
-      <c r="AV98" s="4" t="inlineStr">
+      <c r="AV98" s="4" t="inlineStr"/>
+      <c r="AW98" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW98" s="4" t="inlineStr">
+      <c r="AX98" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX98" s="4" t="inlineStr"/>
       <c r="AY98" s="4" t="inlineStr"/>
       <c r="AZ98" s="4" t="inlineStr"/>
       <c r="BA98" s="4" t="inlineStr"/>
@@ -20786,7 +20944,8 @@
       <c r="BG98" s="4" t="inlineStr"/>
       <c r="BH98" s="4" t="inlineStr"/>
       <c r="BI98" s="4" t="inlineStr"/>
-      <c r="BJ98" s="4" t="inlineStr">
+      <c r="BJ98" s="4" t="inlineStr"/>
+      <c r="BK98" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -20942,17 +21101,17 @@
         </is>
       </c>
       <c r="AU99" s="4" t="inlineStr"/>
-      <c r="AV99" s="4" t="inlineStr">
+      <c r="AV99" s="4" t="inlineStr"/>
+      <c r="AW99" s="4" t="inlineStr">
         <is>
           <t>contain</t>
         </is>
       </c>
-      <c r="AW99" s="4" t="inlineStr">
+      <c r="AX99" s="4" t="inlineStr">
         <is>
           <t>center bottom</t>
         </is>
       </c>
-      <c r="AX99" s="4" t="inlineStr"/>
       <c r="AY99" s="4" t="inlineStr"/>
       <c r="AZ99" s="4" t="inlineStr"/>
       <c r="BA99" s="4" t="inlineStr"/>
@@ -20964,7 +21123,8 @@
       <c r="BG99" s="4" t="inlineStr"/>
       <c r="BH99" s="4" t="inlineStr"/>
       <c r="BI99" s="4" t="inlineStr"/>
-      <c r="BJ99" s="4" t="inlineStr">
+      <c r="BJ99" s="4" t="inlineStr"/>
+      <c r="BK99" s="4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -21053,47 +21213,218 @@
       <c r="BH100" s="4" t="inlineStr"/>
       <c r="BI100" s="4" t="inlineStr"/>
       <c r="BJ100" s="4" t="inlineStr"/>
+      <c r="BK100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101" ht="49.92" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>097</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr"/>
+      <c r="C101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_gravekeeper_offset_body.webp</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr"/>
+      <c r="L101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="4" t="inlineStr"/>
+      <c r="P101" s="4" t="inlineStr"/>
+      <c r="Q101" s="4" t="inlineStr"/>
+      <c r="R101" s="4" t="inlineStr"/>
+      <c r="S101" s="4" t="inlineStr"/>
+      <c r="T101" s="4" t="inlineStr"/>
+      <c r="U101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="4" t="inlineStr"/>
+      <c r="AB101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AD101" s="4" t="inlineStr"/>
+      <c r="AE101" s="4" t="inlineStr"/>
+      <c r="AF101" s="4" t="inlineStr"/>
+      <c r="AG101" s="4" t="inlineStr"/>
+      <c r="AH101" s="4" t="inlineStr"/>
+      <c r="AI101" s="4" t="inlineStr"/>
+      <c r="AJ101" s="4" t="inlineStr"/>
+      <c r="AK101" s="4" t="inlineStr"/>
+      <c r="AL101" s="4" t="inlineStr"/>
+      <c r="AM101" s="4" t="inlineStr"/>
+      <c r="AN101" s="4" t="inlineStr"/>
+      <c r="AO101" s="4" t="inlineStr"/>
+      <c r="AP101" s="4" t="inlineStr"/>
+      <c r="AQ101" s="4" t="inlineStr"/>
+      <c r="AR101" s="4" t="inlineStr"/>
+      <c r="AS101" s="4" t="inlineStr"/>
+      <c r="AT101" s="4" t="inlineStr"/>
+      <c r="AU101" s="4" t="inlineStr"/>
+      <c r="AV101" s="4" t="inlineStr"/>
+      <c r="AW101" s="4" t="inlineStr"/>
+      <c r="AX101" s="4" t="inlineStr"/>
+      <c r="AY101" s="4" t="inlineStr"/>
+      <c r="AZ101" s="4" t="inlineStr"/>
+      <c r="BA101" s="4" t="inlineStr"/>
+      <c r="BB101" s="4" t="inlineStr"/>
+      <c r="BC101" s="4" t="inlineStr"/>
+      <c r="BD101" s="4" t="inlineStr"/>
+      <c r="BE101" s="4" t="inlineStr"/>
+      <c r="BF101" s="4" t="inlineStr"/>
+      <c r="BG101" s="4" t="inlineStr"/>
+      <c r="BH101" s="4" t="inlineStr"/>
+      <c r="BI101" s="4" t="inlineStr"/>
+      <c r="BJ101" s="4" t="inlineStr"/>
+      <c r="BK101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102" ht="49.92" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>098</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr"/>
+      <c r="C102" s="4" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_gravekeeper_offset_soul.webp</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr"/>
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr"/>
+      <c r="P102" s="4" t="inlineStr"/>
+      <c r="Q102" s="4" t="inlineStr"/>
+      <c r="R102" s="4" t="inlineStr"/>
+      <c r="S102" s="4" t="inlineStr"/>
+      <c r="T102" s="4" t="inlineStr"/>
+      <c r="U102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="4" t="inlineStr"/>
+      <c r="AB102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AD102" s="4" t="inlineStr"/>
+      <c r="AE102" s="4" t="inlineStr"/>
+      <c r="AF102" s="4" t="inlineStr"/>
+      <c r="AG102" s="4" t="inlineStr"/>
+      <c r="AH102" s="4" t="inlineStr"/>
+      <c r="AI102" s="4" t="inlineStr"/>
+      <c r="AJ102" s="4" t="inlineStr"/>
+      <c r="AK102" s="4" t="inlineStr"/>
+      <c r="AL102" s="4" t="inlineStr"/>
+      <c r="AM102" s="4" t="inlineStr"/>
+      <c r="AN102" s="4" t="inlineStr"/>
+      <c r="AO102" s="4" t="inlineStr"/>
+      <c r="AP102" s="4" t="inlineStr"/>
+      <c r="AQ102" s="4" t="inlineStr"/>
+      <c r="AR102" s="4" t="inlineStr"/>
+      <c r="AS102" s="4" t="inlineStr"/>
+      <c r="AT102" s="4" t="inlineStr"/>
+      <c r="AU102" s="4" t="inlineStr"/>
+      <c r="AV102" s="4" t="inlineStr"/>
+      <c r="AW102" s="4" t="inlineStr"/>
+      <c r="AX102" s="4" t="inlineStr"/>
+      <c r="AY102" s="4" t="inlineStr"/>
+      <c r="AZ102" s="4" t="inlineStr"/>
+      <c r="BA102" s="4" t="inlineStr"/>
+      <c r="BB102" s="4" t="inlineStr"/>
+      <c r="BC102" s="4" t="inlineStr"/>
+      <c r="BD102" s="4" t="inlineStr"/>
+      <c r="BE102" s="4" t="inlineStr"/>
+      <c r="BF102" s="4" t="inlineStr"/>
+      <c r="BG102" s="4" t="inlineStr"/>
+      <c r="BH102" s="4" t="inlineStr"/>
+      <c r="BI102" s="4" t="inlineStr"/>
+      <c r="BJ102" s="4" t="inlineStr"/>
+      <c r="BK102" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="AY1:BJ1"/>
     <mergeCell ref="F1:R1"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AD1:AH1"/>
+    <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="S1:Z1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AH1"/>
-    <mergeCell ref="AI1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AR1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AX1:BI1"/>
-    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="AR1:AV1"/>
+    <mergeCell ref="AW1:AX1"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="Q4:Q100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="Q4:Q102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$A$2:$A$17</formula1>
     </dataValidation>
-    <dataValidation sqref="AX4:AX100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AY4:AY102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BA4:BA100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BB4:BB102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BD4:BD100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BE4:BE102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BG4:BG100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BH4:BH102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="AR4:AR100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AR4:AR102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation sqref="AS4:AS100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AS4:AS102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation sqref="AT4:AT100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AT4:AT102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation sqref="AU4:AU100" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AU4:AU102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -21656,7 +21987,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>7066a681f4922c878ac2b04d6472de10fc9ee2684f1895a09694c2bd09c7fef5</t>
+          <t>ae79870fc7f3df57b4b0f157386e80f3ccb902aabe2bc5ddf6401635af44c3a5</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -1052,7 +1052,7 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="866775"/>
+    <ext cx="609600" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -2602,7 +2602,7 @@
       <row>100</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="762000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="98" name="Image 98" descr="Picture"/>
@@ -2627,7 +2627,7 @@
       <row>101</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="99" name="Image 99" descr="Picture"/>
@@ -2635,6 +2635,231 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="914400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="914400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="914400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="914400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="914400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2937,7 +3162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL102"/>
+  <dimension ref="A1:BL111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10108,7 +10333,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="70.98" customHeight="1">
+    <row r="39" ht="58.5" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>035</t>
@@ -21436,29 +21661,67 @@
           <t>096</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>ph_sword_angel</t>
+        </is>
+      </c>
       <c r="C100" s="4" t="inlineStr"/>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_dragon_throne_dormant.webp</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr"/>
-      <c r="O100" s="4" t="inlineStr"/>
-      <c r="P100" s="4" t="inlineStr"/>
+          <t>resources/enemy/phamtoms/ph_sword_angel.webp</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>執劍天使</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M100" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q100" s="4" t="inlineStr"/>
       <c r="R100" s="4" t="inlineStr"/>
       <c r="S100" s="4" t="inlineStr"/>
-      <c r="T100" s="4" t="inlineStr"/>
+      <c r="T100" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="U100" s="4" t="inlineStr"/>
       <c r="V100" s="4" t="n">
         <v>0</v>
@@ -21478,30 +21741,80 @@
       <c r="AA100" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AB100" s="4" t="inlineStr"/>
-      <c r="AC100" s="4" t="inlineStr"/>
-      <c r="AD100" s="4" t="inlineStr"/>
+      <c r="AB100" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD100" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="AE100" s="4" t="inlineStr"/>
-      <c r="AF100" s="4" t="inlineStr"/>
-      <c r="AG100" s="4" t="inlineStr"/>
-      <c r="AH100" s="4" t="inlineStr"/>
-      <c r="AI100" s="4" t="inlineStr"/>
-      <c r="AJ100" s="4" t="inlineStr"/>
-      <c r="AK100" s="4" t="inlineStr"/>
-      <c r="AL100" s="4" t="inlineStr"/>
-      <c r="AM100" s="4" t="inlineStr"/>
-      <c r="AN100" s="4" t="inlineStr"/>
-      <c r="AO100" s="4" t="inlineStr"/>
-      <c r="AP100" s="4" t="inlineStr"/>
+      <c r="AF100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK100" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL100" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM100" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO100" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP100" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AQ100" s="4" t="inlineStr"/>
       <c r="AR100" s="4" t="inlineStr"/>
-      <c r="AS100" s="4" t="inlineStr"/>
-      <c r="AT100" s="4" t="inlineStr"/>
-      <c r="AU100" s="4" t="inlineStr"/>
+      <c r="AS100" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT100" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU100" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
       <c r="AV100" s="4" t="inlineStr"/>
       <c r="AW100" s="4" t="inlineStr"/>
-      <c r="AX100" s="4" t="inlineStr"/>
-      <c r="AY100" s="4" t="inlineStr"/>
+      <c r="AX100" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY100" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="AZ100" s="4" t="inlineStr"/>
       <c r="BA100" s="4" t="inlineStr"/>
       <c r="BB100" s="4" t="inlineStr"/>
@@ -21514,37 +21827,79 @@
       <c r="BI100" s="4" t="inlineStr"/>
       <c r="BJ100" s="4" t="inlineStr"/>
       <c r="BK100" s="4" t="inlineStr"/>
-      <c r="BL100" s="4" t="inlineStr"/>
+      <c r="BL100" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
-    <row r="101" ht="49.92" customHeight="1">
+    <row r="101" ht="62.40000000000001" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
           <t>097</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr"/>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>ph_mercy_remnant</t>
+        </is>
+      </c>
       <c r="C101" s="4" t="inlineStr"/>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_gravekeeper_offset_body.webp</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
-      <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr"/>
-      <c r="M101" s="4" t="inlineStr"/>
-      <c r="N101" s="4" t="inlineStr"/>
-      <c r="O101" s="4" t="inlineStr"/>
-      <c r="P101" s="4" t="inlineStr"/>
+          <t>resources/enemy/phamtoms/ph_mercy_remnant.webp</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>慈愛殘像</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M101" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q101" s="4" t="inlineStr"/>
       <c r="R101" s="4" t="inlineStr"/>
       <c r="S101" s="4" t="inlineStr"/>
-      <c r="T101" s="4" t="inlineStr"/>
+      <c r="T101" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="U101" s="4" t="inlineStr"/>
       <c r="V101" s="4" t="n">
         <v>0</v>
@@ -21564,30 +21919,80 @@
       <c r="AA101" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AB101" s="4" t="inlineStr"/>
-      <c r="AC101" s="4" t="inlineStr"/>
-      <c r="AD101" s="4" t="inlineStr"/>
+      <c r="AB101" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="AE101" s="4" t="inlineStr"/>
-      <c r="AF101" s="4" t="inlineStr"/>
-      <c r="AG101" s="4" t="inlineStr"/>
-      <c r="AH101" s="4" t="inlineStr"/>
-      <c r="AI101" s="4" t="inlineStr"/>
-      <c r="AJ101" s="4" t="inlineStr"/>
-      <c r="AK101" s="4" t="inlineStr"/>
-      <c r="AL101" s="4" t="inlineStr"/>
-      <c r="AM101" s="4" t="inlineStr"/>
-      <c r="AN101" s="4" t="inlineStr"/>
-      <c r="AO101" s="4" t="inlineStr"/>
-      <c r="AP101" s="4" t="inlineStr"/>
+      <c r="AF101" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG101" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK101" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL101" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM101" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO101" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP101" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AQ101" s="4" t="inlineStr"/>
       <c r="AR101" s="4" t="inlineStr"/>
-      <c r="AS101" s="4" t="inlineStr"/>
-      <c r="AT101" s="4" t="inlineStr"/>
-      <c r="AU101" s="4" t="inlineStr"/>
+      <c r="AS101" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT101" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU101" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
       <c r="AV101" s="4" t="inlineStr"/>
       <c r="AW101" s="4" t="inlineStr"/>
-      <c r="AX101" s="4" t="inlineStr"/>
-      <c r="AY101" s="4" t="inlineStr"/>
+      <c r="AX101" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY101" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="AZ101" s="4" t="inlineStr"/>
       <c r="BA101" s="4" t="inlineStr"/>
       <c r="BB101" s="4" t="inlineStr"/>
@@ -21600,37 +22005,79 @@
       <c r="BI101" s="4" t="inlineStr"/>
       <c r="BJ101" s="4" t="inlineStr"/>
       <c r="BK101" s="4" t="inlineStr"/>
-      <c r="BL101" s="4" t="inlineStr"/>
+      <c r="BL101" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
-    <row r="102" ht="49.92" customHeight="1">
+    <row r="102" ht="74.88" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
           <t>098</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr"/>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>ph_gifted</t>
+        </is>
+      </c>
       <c r="C102" s="4" t="inlineStr"/>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_gravekeeper_offset_soul.webp</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr"/>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr"/>
-      <c r="J102" s="4" t="inlineStr"/>
-      <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr"/>
-      <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr"/>
-      <c r="O102" s="4" t="inlineStr"/>
-      <c r="P102" s="4" t="inlineStr"/>
+          <t>resources/enemy/phamtoms/ph_gifted.webp</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>才能祝福之人</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M102" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q102" s="4" t="inlineStr"/>
       <c r="R102" s="4" t="inlineStr"/>
       <c r="S102" s="4" t="inlineStr"/>
-      <c r="T102" s="4" t="inlineStr"/>
+      <c r="T102" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="U102" s="4" t="inlineStr"/>
       <c r="V102" s="4" t="n">
         <v>0</v>
@@ -21650,30 +22097,80 @@
       <c r="AA102" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AB102" s="4" t="inlineStr"/>
-      <c r="AC102" s="4" t="inlineStr"/>
-      <c r="AD102" s="4" t="inlineStr"/>
+      <c r="AB102" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD102" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="AE102" s="4" t="inlineStr"/>
-      <c r="AF102" s="4" t="inlineStr"/>
-      <c r="AG102" s="4" t="inlineStr"/>
-      <c r="AH102" s="4" t="inlineStr"/>
-      <c r="AI102" s="4" t="inlineStr"/>
-      <c r="AJ102" s="4" t="inlineStr"/>
-      <c r="AK102" s="4" t="inlineStr"/>
-      <c r="AL102" s="4" t="inlineStr"/>
-      <c r="AM102" s="4" t="inlineStr"/>
-      <c r="AN102" s="4" t="inlineStr"/>
-      <c r="AO102" s="4" t="inlineStr"/>
-      <c r="AP102" s="4" t="inlineStr"/>
+      <c r="AF102" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK102" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL102" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM102" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO102" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP102" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AQ102" s="4" t="inlineStr"/>
       <c r="AR102" s="4" t="inlineStr"/>
-      <c r="AS102" s="4" t="inlineStr"/>
-      <c r="AT102" s="4" t="inlineStr"/>
-      <c r="AU102" s="4" t="inlineStr"/>
+      <c r="AS102" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT102" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU102" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
       <c r="AV102" s="4" t="inlineStr"/>
       <c r="AW102" s="4" t="inlineStr"/>
-      <c r="AX102" s="4" t="inlineStr"/>
-      <c r="AY102" s="4" t="inlineStr"/>
+      <c r="AX102" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY102" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="AZ102" s="4" t="inlineStr"/>
       <c r="BA102" s="4" t="inlineStr"/>
       <c r="BB102" s="4" t="inlineStr"/>
@@ -21686,48 +22183,1286 @@
       <c r="BI102" s="4" t="inlineStr"/>
       <c r="BJ102" s="4" t="inlineStr"/>
       <c r="BK102" s="4" t="inlineStr"/>
-      <c r="BL102" s="4" t="inlineStr"/>
+      <c r="BL102" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="74.88" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>099</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>ph_slaughter_witch</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/phamtoms/ph_slaughter_witch.webp</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>殺戮魔女</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M103" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="4" t="inlineStr"/>
+      <c r="R103" s="4" t="inlineStr"/>
+      <c r="S103" s="4" t="inlineStr"/>
+      <c r="T103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="4" t="inlineStr"/>
+      <c r="V103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD103" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE103" s="4" t="inlineStr"/>
+      <c r="AF103" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK103" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL103" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM103" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO103" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ103" s="4" t="inlineStr"/>
+      <c r="AR103" s="4" t="inlineStr"/>
+      <c r="AS103" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT103" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU103" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
+      <c r="AV103" s="4" t="inlineStr"/>
+      <c r="AW103" s="4" t="inlineStr"/>
+      <c r="AX103" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY103" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
+      <c r="AZ103" s="4" t="inlineStr"/>
+      <c r="BA103" s="4" t="inlineStr"/>
+      <c r="BB103" s="4" t="inlineStr"/>
+      <c r="BC103" s="4" t="inlineStr"/>
+      <c r="BD103" s="4" t="inlineStr"/>
+      <c r="BE103" s="4" t="inlineStr"/>
+      <c r="BF103" s="4" t="inlineStr"/>
+      <c r="BG103" s="4" t="inlineStr"/>
+      <c r="BH103" s="4" t="inlineStr"/>
+      <c r="BI103" s="4" t="inlineStr"/>
+      <c r="BJ103" s="4" t="inlineStr"/>
+      <c r="BK103" s="4" t="inlineStr"/>
+      <c r="BL103" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="62.40000000000001" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>ph_hairbound</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/phamtoms/ph_hairbound.webp</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>纏髮之人</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M104" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="4" t="inlineStr"/>
+      <c r="R104" s="4" t="inlineStr"/>
+      <c r="S104" s="4" t="inlineStr"/>
+      <c r="T104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="4" t="inlineStr"/>
+      <c r="V104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE104" s="4" t="inlineStr"/>
+      <c r="AF104" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG104" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK104" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL104" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM104" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO104" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP104" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ104" s="4" t="inlineStr"/>
+      <c r="AR104" s="4" t="inlineStr"/>
+      <c r="AS104" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT104" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU104" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
+      <c r="AV104" s="4" t="inlineStr"/>
+      <c r="AW104" s="4" t="inlineStr"/>
+      <c r="AX104" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY104" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
+      <c r="AZ104" s="4" t="inlineStr"/>
+      <c r="BA104" s="4" t="inlineStr"/>
+      <c r="BB104" s="4" t="inlineStr"/>
+      <c r="BC104" s="4" t="inlineStr"/>
+      <c r="BD104" s="4" t="inlineStr"/>
+      <c r="BE104" s="4" t="inlineStr"/>
+      <c r="BF104" s="4" t="inlineStr"/>
+      <c r="BG104" s="4" t="inlineStr"/>
+      <c r="BH104" s="4" t="inlineStr"/>
+      <c r="BI104" s="4" t="inlineStr"/>
+      <c r="BJ104" s="4" t="inlineStr"/>
+      <c r="BK104" s="4" t="inlineStr"/>
+      <c r="BL104" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="74.88" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>ph_coffin_bearer</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/phamtoms/ph_coffin_bearer.webp</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>負棺者</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M105" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="4" t="inlineStr"/>
+      <c r="R105" s="4" t="inlineStr"/>
+      <c r="S105" s="4" t="inlineStr"/>
+      <c r="T105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="4" t="inlineStr"/>
+      <c r="V105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD105" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE105" s="4" t="inlineStr"/>
+      <c r="AF105" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG105" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK105" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL105" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM105" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO105" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP105" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ105" s="4" t="inlineStr"/>
+      <c r="AR105" s="4" t="inlineStr"/>
+      <c r="AS105" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT105" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU105" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
+      <c r="AV105" s="4" t="inlineStr"/>
+      <c r="AW105" s="4" t="inlineStr"/>
+      <c r="AX105" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY105" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
+      <c r="AZ105" s="4" t="inlineStr"/>
+      <c r="BA105" s="4" t="inlineStr"/>
+      <c r="BB105" s="4" t="inlineStr"/>
+      <c r="BC105" s="4" t="inlineStr"/>
+      <c r="BD105" s="4" t="inlineStr"/>
+      <c r="BE105" s="4" t="inlineStr"/>
+      <c r="BF105" s="4" t="inlineStr"/>
+      <c r="BG105" s="4" t="inlineStr"/>
+      <c r="BH105" s="4" t="inlineStr"/>
+      <c r="BI105" s="4" t="inlineStr"/>
+      <c r="BJ105" s="4" t="inlineStr"/>
+      <c r="BK105" s="4" t="inlineStr"/>
+      <c r="BL105" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="60.06" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>ph_greed</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/phamtoms/ph_greed.webp</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>貪欲者</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="M106" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="4" t="inlineStr"/>
+      <c r="R106" s="4" t="inlineStr"/>
+      <c r="S106" s="4" t="inlineStr"/>
+      <c r="T106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="4" t="inlineStr"/>
+      <c r="V106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 9, 16]</t>
+        </is>
+      </c>
+      <c r="AC106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE106" s="4" t="inlineStr"/>
+      <c r="AF106" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG106" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK106" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM106" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO106" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP106" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ106" s="4" t="inlineStr"/>
+      <c r="AR106" s="4" t="inlineStr"/>
+      <c r="AS106" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT106" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU106" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
+      <c r="AV106" s="4" t="inlineStr"/>
+      <c r="AW106" s="4" t="inlineStr"/>
+      <c r="AX106" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY106" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
+      <c r="AZ106" s="4" t="inlineStr"/>
+      <c r="BA106" s="4" t="inlineStr"/>
+      <c r="BB106" s="4" t="inlineStr"/>
+      <c r="BC106" s="4" t="inlineStr"/>
+      <c r="BD106" s="4" t="inlineStr"/>
+      <c r="BE106" s="4" t="inlineStr"/>
+      <c r="BF106" s="4" t="inlineStr"/>
+      <c r="BG106" s="4" t="inlineStr"/>
+      <c r="BH106" s="4" t="inlineStr"/>
+      <c r="BI106" s="4" t="inlineStr"/>
+      <c r="BJ106" s="4" t="inlineStr"/>
+      <c r="BK106" s="4" t="inlineStr"/>
+      <c r="BL106" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="74.88" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>ph_silent_waiter</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/phamtoms/ph_silent_waiter.webp</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>靜默等待者</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>harm</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="M107" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="4" t="inlineStr"/>
+      <c r="R107" s="4" t="inlineStr"/>
+      <c r="S107" s="4" t="inlineStr"/>
+      <c r="T107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="4" t="inlineStr"/>
+      <c r="V107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="4" t="inlineStr">
+        <is>
+          <t>[9, 9, 9, 16, 16]</t>
+        </is>
+      </c>
+      <c r="AC107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD107" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE107" s="4" t="inlineStr"/>
+      <c r="AF107" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG107" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK107" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL107" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM107" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO107" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP107" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ107" s="4" t="inlineStr"/>
+      <c r="AR107" s="4" t="inlineStr"/>
+      <c r="AS107" s="4" t="inlineStr">
+        <is>
+          <t>claw1</t>
+        </is>
+      </c>
+      <c r="AT107" s="4" t="inlineStr">
+        <is>
+          <t>bite</t>
+        </is>
+      </c>
+      <c r="AU107" s="4" t="inlineStr">
+        <is>
+          <t>claw</t>
+        </is>
+      </c>
+      <c r="AV107" s="4" t="inlineStr"/>
+      <c r="AW107" s="4" t="inlineStr"/>
+      <c r="AX107" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AY107" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
+      <c r="AZ107" s="4" t="inlineStr"/>
+      <c r="BA107" s="4" t="inlineStr"/>
+      <c r="BB107" s="4" t="inlineStr"/>
+      <c r="BC107" s="4" t="inlineStr"/>
+      <c r="BD107" s="4" t="inlineStr"/>
+      <c r="BE107" s="4" t="inlineStr"/>
+      <c r="BF107" s="4" t="inlineStr"/>
+      <c r="BG107" s="4" t="inlineStr"/>
+      <c r="BH107" s="4" t="inlineStr"/>
+      <c r="BI107" s="4" t="inlineStr"/>
+      <c r="BJ107" s="4" t="inlineStr"/>
+      <c r="BK107" s="4" t="inlineStr"/>
+      <c r="BL107" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="74.88" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr"/>
+      <c r="C108" s="4" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_dragon_throne_dormant.webp</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr"/>
+      <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr"/>
+      <c r="P108" s="4" t="inlineStr"/>
+      <c r="Q108" s="4" t="inlineStr"/>
+      <c r="R108" s="4" t="inlineStr"/>
+      <c r="S108" s="4" t="inlineStr"/>
+      <c r="T108" s="4" t="inlineStr"/>
+      <c r="U108" s="4" t="inlineStr"/>
+      <c r="V108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AD108" s="4" t="inlineStr"/>
+      <c r="AE108" s="4" t="inlineStr"/>
+      <c r="AF108" s="4" t="inlineStr"/>
+      <c r="AG108" s="4" t="inlineStr"/>
+      <c r="AH108" s="4" t="inlineStr"/>
+      <c r="AI108" s="4" t="inlineStr"/>
+      <c r="AJ108" s="4" t="inlineStr"/>
+      <c r="AK108" s="4" t="inlineStr"/>
+      <c r="AL108" s="4" t="inlineStr"/>
+      <c r="AM108" s="4" t="inlineStr"/>
+      <c r="AN108" s="4" t="inlineStr"/>
+      <c r="AO108" s="4" t="inlineStr"/>
+      <c r="AP108" s="4" t="inlineStr"/>
+      <c r="AQ108" s="4" t="inlineStr"/>
+      <c r="AR108" s="4" t="inlineStr"/>
+      <c r="AS108" s="4" t="inlineStr"/>
+      <c r="AT108" s="4" t="inlineStr"/>
+      <c r="AU108" s="4" t="inlineStr"/>
+      <c r="AV108" s="4" t="inlineStr"/>
+      <c r="AW108" s="4" t="inlineStr"/>
+      <c r="AX108" s="4" t="inlineStr"/>
+      <c r="AY108" s="4" t="inlineStr"/>
+      <c r="AZ108" s="4" t="inlineStr"/>
+      <c r="BA108" s="4" t="inlineStr"/>
+      <c r="BB108" s="4" t="inlineStr"/>
+      <c r="BC108" s="4" t="inlineStr"/>
+      <c r="BD108" s="4" t="inlineStr"/>
+      <c r="BE108" s="4" t="inlineStr"/>
+      <c r="BF108" s="4" t="inlineStr"/>
+      <c r="BG108" s="4" t="inlineStr"/>
+      <c r="BH108" s="4" t="inlineStr"/>
+      <c r="BI108" s="4" t="inlineStr"/>
+      <c r="BJ108" s="4" t="inlineStr"/>
+      <c r="BK108" s="4" t="inlineStr"/>
+      <c r="BL108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109" ht="49.92" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr"/>
+      <c r="C109" s="4" t="inlineStr"/>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_gravekeeper_offset_body.webp</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
+      <c r="G109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+      <c r="M109" s="4" t="inlineStr"/>
+      <c r="N109" s="4" t="inlineStr"/>
+      <c r="O109" s="4" t="inlineStr"/>
+      <c r="P109" s="4" t="inlineStr"/>
+      <c r="Q109" s="4" t="inlineStr"/>
+      <c r="R109" s="4" t="inlineStr"/>
+      <c r="S109" s="4" t="inlineStr"/>
+      <c r="T109" s="4" t="inlineStr"/>
+      <c r="U109" s="4" t="inlineStr"/>
+      <c r="V109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AD109" s="4" t="inlineStr"/>
+      <c r="AE109" s="4" t="inlineStr"/>
+      <c r="AF109" s="4" t="inlineStr"/>
+      <c r="AG109" s="4" t="inlineStr"/>
+      <c r="AH109" s="4" t="inlineStr"/>
+      <c r="AI109" s="4" t="inlineStr"/>
+      <c r="AJ109" s="4" t="inlineStr"/>
+      <c r="AK109" s="4" t="inlineStr"/>
+      <c r="AL109" s="4" t="inlineStr"/>
+      <c r="AM109" s="4" t="inlineStr"/>
+      <c r="AN109" s="4" t="inlineStr"/>
+      <c r="AO109" s="4" t="inlineStr"/>
+      <c r="AP109" s="4" t="inlineStr"/>
+      <c r="AQ109" s="4" t="inlineStr"/>
+      <c r="AR109" s="4" t="inlineStr"/>
+      <c r="AS109" s="4" t="inlineStr"/>
+      <c r="AT109" s="4" t="inlineStr"/>
+      <c r="AU109" s="4" t="inlineStr"/>
+      <c r="AV109" s="4" t="inlineStr"/>
+      <c r="AW109" s="4" t="inlineStr"/>
+      <c r="AX109" s="4" t="inlineStr"/>
+      <c r="AY109" s="4" t="inlineStr"/>
+      <c r="AZ109" s="4" t="inlineStr"/>
+      <c r="BA109" s="4" t="inlineStr"/>
+      <c r="BB109" s="4" t="inlineStr"/>
+      <c r="BC109" s="4" t="inlineStr"/>
+      <c r="BD109" s="4" t="inlineStr"/>
+      <c r="BE109" s="4" t="inlineStr"/>
+      <c r="BF109" s="4" t="inlineStr"/>
+      <c r="BG109" s="4" t="inlineStr"/>
+      <c r="BH109" s="4" t="inlineStr"/>
+      <c r="BI109" s="4" t="inlineStr"/>
+      <c r="BJ109" s="4" t="inlineStr"/>
+      <c r="BK109" s="4" t="inlineStr"/>
+      <c r="BL109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110" ht="49.92" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr"/>
+      <c r="C110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_gravekeeper_offset_soul.webp</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr"/>
+      <c r="P110" s="4" t="inlineStr"/>
+      <c r="Q110" s="4" t="inlineStr"/>
+      <c r="R110" s="4" t="inlineStr"/>
+      <c r="S110" s="4" t="inlineStr"/>
+      <c r="T110" s="4" t="inlineStr"/>
+      <c r="U110" s="4" t="inlineStr"/>
+      <c r="V110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AD110" s="4" t="inlineStr"/>
+      <c r="AE110" s="4" t="inlineStr"/>
+      <c r="AF110" s="4" t="inlineStr"/>
+      <c r="AG110" s="4" t="inlineStr"/>
+      <c r="AH110" s="4" t="inlineStr"/>
+      <c r="AI110" s="4" t="inlineStr"/>
+      <c r="AJ110" s="4" t="inlineStr"/>
+      <c r="AK110" s="4" t="inlineStr"/>
+      <c r="AL110" s="4" t="inlineStr"/>
+      <c r="AM110" s="4" t="inlineStr"/>
+      <c r="AN110" s="4" t="inlineStr"/>
+      <c r="AO110" s="4" t="inlineStr"/>
+      <c r="AP110" s="4" t="inlineStr"/>
+      <c r="AQ110" s="4" t="inlineStr"/>
+      <c r="AR110" s="4" t="inlineStr"/>
+      <c r="AS110" s="4" t="inlineStr"/>
+      <c r="AT110" s="4" t="inlineStr"/>
+      <c r="AU110" s="4" t="inlineStr"/>
+      <c r="AV110" s="4" t="inlineStr"/>
+      <c r="AW110" s="4" t="inlineStr"/>
+      <c r="AX110" s="4" t="inlineStr"/>
+      <c r="AY110" s="4" t="inlineStr"/>
+      <c r="AZ110" s="4" t="inlineStr"/>
+      <c r="BA110" s="4" t="inlineStr"/>
+      <c r="BB110" s="4" t="inlineStr"/>
+      <c r="BC110" s="4" t="inlineStr"/>
+      <c r="BD110" s="4" t="inlineStr"/>
+      <c r="BE110" s="4" t="inlineStr"/>
+      <c r="BF110" s="4" t="inlineStr"/>
+      <c r="BG110" s="4" t="inlineStr"/>
+      <c r="BH110" s="4" t="inlineStr"/>
+      <c r="BI110" s="4" t="inlineStr"/>
+      <c r="BJ110" s="4" t="inlineStr"/>
+      <c r="BK110" s="4" t="inlineStr"/>
+      <c r="BL110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111" ht="74.88" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr"/>
+      <c r="C111" s="4" t="inlineStr"/>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_gravekeeper_seal_down.webp</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr"/>
+      <c r="O111" s="4" t="inlineStr"/>
+      <c r="P111" s="4" t="inlineStr"/>
+      <c r="Q111" s="4" t="inlineStr"/>
+      <c r="R111" s="4" t="inlineStr"/>
+      <c r="S111" s="4" t="inlineStr"/>
+      <c r="T111" s="4" t="inlineStr"/>
+      <c r="U111" s="4" t="inlineStr"/>
+      <c r="V111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AD111" s="4" t="inlineStr"/>
+      <c r="AE111" s="4" t="inlineStr"/>
+      <c r="AF111" s="4" t="inlineStr"/>
+      <c r="AG111" s="4" t="inlineStr"/>
+      <c r="AH111" s="4" t="inlineStr"/>
+      <c r="AI111" s="4" t="inlineStr"/>
+      <c r="AJ111" s="4" t="inlineStr"/>
+      <c r="AK111" s="4" t="inlineStr"/>
+      <c r="AL111" s="4" t="inlineStr"/>
+      <c r="AM111" s="4" t="inlineStr"/>
+      <c r="AN111" s="4" t="inlineStr"/>
+      <c r="AO111" s="4" t="inlineStr"/>
+      <c r="AP111" s="4" t="inlineStr"/>
+      <c r="AQ111" s="4" t="inlineStr"/>
+      <c r="AR111" s="4" t="inlineStr"/>
+      <c r="AS111" s="4" t="inlineStr"/>
+      <c r="AT111" s="4" t="inlineStr"/>
+      <c r="AU111" s="4" t="inlineStr"/>
+      <c r="AV111" s="4" t="inlineStr"/>
+      <c r="AW111" s="4" t="inlineStr"/>
+      <c r="AX111" s="4" t="inlineStr"/>
+      <c r="AY111" s="4" t="inlineStr"/>
+      <c r="AZ111" s="4" t="inlineStr"/>
+      <c r="BA111" s="4" t="inlineStr"/>
+      <c r="BB111" s="4" t="inlineStr"/>
+      <c r="BC111" s="4" t="inlineStr"/>
+      <c r="BD111" s="4" t="inlineStr"/>
+      <c r="BE111" s="4" t="inlineStr"/>
+      <c r="BF111" s="4" t="inlineStr"/>
+      <c r="BG111" s="4" t="inlineStr"/>
+      <c r="BH111" s="4" t="inlineStr"/>
+      <c r="BI111" s="4" t="inlineStr"/>
+      <c r="BJ111" s="4" t="inlineStr"/>
+      <c r="BK111" s="4" t="inlineStr"/>
+      <c r="BL111" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:S1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="AZ1:BK1"/>
-    <mergeCell ref="AE1:AI1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="A1:A3"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="R4:R102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'__lists__'!$A$2:$A$17</formula1>
+    <dataValidation sqref="R4:R111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+      <formula1>'__lists__'!$A$2:$A$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AZ4:AZ102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ4:AZ111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BC4:BC102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BC4:BC111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BF4:BF102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BF4:BF111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BI4:BI102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BI4:BI111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="AS4:AS102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AS4:AS111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation sqref="AT4:AT102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AT4:AT111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation sqref="AU4:AU102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AU4:AU111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation sqref="AV4:AV102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV4:AV111" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -21765,7 +23500,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kerberos</t>
+          <t>_dunmor_batch1_sheet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -21782,7 +23517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sentouinstall</t>
+          <t>_dunmor_batch2_stopped_sheet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -21799,7 +23534,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sky_cirrus_dawn</t>
+          <t>_dunmor_batch3_sheet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -21816,7 +23551,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sky_cirrus_day</t>
+          <t>kerberos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -21833,7 +23568,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sky_cirrus_dusk</t>
+          <t>sentouinstall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -21850,7 +23585,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sky_cirrus_night</t>
+          <t>sky_cirrus_dawn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -21867,7 +23602,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sky_cumulus_dawn</t>
+          <t>sky_cirrus_day</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -21884,7 +23619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sky_cumulus_day</t>
+          <t>sky_cirrus_dusk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -21901,7 +23636,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sky_cumulus_dusk</t>
+          <t>sky_cirrus_night</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -21918,7 +23653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sky_cumulus_night</t>
+          <t>sky_cumulus_dawn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -21935,7 +23670,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sky_towers</t>
+          <t>sky_cumulus_day</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -21952,7 +23687,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sky_towers_dawn</t>
+          <t>sky_cumulus_dusk</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21969,7 +23704,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sky_towers_day</t>
+          <t>sky_cumulus_night</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -21986,7 +23721,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sky_towers_dusk</t>
+          <t>sky_towers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -22003,7 +23738,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sky_towers_night</t>
+          <t>sky_towers_dawn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -22020,7 +23755,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tivot_emblem</t>
+          <t>sky_towers_day</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -22035,6 +23770,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sky_towers_dusk</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>河芹｜veg_watercress</t>
@@ -22047,6 +23787,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sky_towers_night</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>草原奶油｜season_butter</t>
@@ -22059,6 +23804,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tivot_emblem</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>北峰山羊奶油｜season_goatbutter</t>
@@ -22290,7 +24040,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>8db5a0e20296094d0b4c9d62b2e0b0e5c500eb554d222492e5ea33d77bb57f15</t>
+          <t>ed88d5daceb704d020730bf349bc619ec3bbfb71ef0a9c4c0b6b3f35bcf70f24</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rayku/Desktop/TIVOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{6FF0C614-0495-BC4E-8A94-E9F871A39E4F}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{7D648839-2BB4-AA4C-8848-8EA8ADCBEEF7}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6980" yWindow="4160" windowWidth="51200" windowHeight="26420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="敵人卡" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="721">
   <si>
     <t>編號</t>
   </si>
@@ -2182,6 +2182,10 @@
   </si>
   <si>
     <t>這一頁不要改。匯入時會拿它確認「你手上這份是從哪一版匯出的」。</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -15902,7 +15906,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>177</v>
+        <v>720</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>133</v>
@@ -24472,17 +24476,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="AZ1:BK1"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:S1"/>
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="AB1:AD1"/>
     <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rayku/Desktop/TIVOT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{7D648839-2BB4-AA4C-8848-8EA8ADCBEEF7}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{125184A9-D11B-034B-9372-A2393F4012FF}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6980" yWindow="4160" windowWidth="51200" windowHeight="26420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13780" yWindow="1480" windowWidth="51200" windowHeight="26420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="敵人卡" sheetId="1" r:id="rId1"/>
@@ -15915,7 +15915,7 @@
         <v>1</v>
       </c>
       <c r="L62" s="4">
-        <v>730</v>
+        <v>450</v>
       </c>
       <c r="M62" s="4">
         <v>20</v>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -813,7 +813,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -838,7 +838,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -863,7 +863,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -888,7 +888,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -913,7 +913,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -938,7 +938,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -963,7 +963,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -988,7 +988,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1013,7 +1013,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1038,10 +1038,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="809625"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1063,10 +1063,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="485775"/>
+    <ext cx="609600" cy="809625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1088,10 +1088,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="409575"/>
+    <ext cx="609600" cy="485775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1113,10 +1113,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="409575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1138,10 +1138,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="904875"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1163,10 +1163,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="409575"/>
+    <ext cx="609600" cy="904875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1188,7 +1188,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="409575"/>
@@ -1213,10 +1213,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="409575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1238,10 +1238,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="647700"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1263,10 +1263,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1288,10 +1288,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="895350"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1313,10 +1313,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="714375"/>
+    <ext cx="609600" cy="895350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -1338,10 +1338,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="47" name="Image 47" descr="Picture"/>
@@ -1363,10 +1363,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="904875"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="48" name="Image 48" descr="Picture"/>
@@ -1388,10 +1388,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="628650"/>
+    <ext cx="609600" cy="904875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -1413,10 +1413,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="904875"/>
+    <ext cx="609600" cy="628650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -1438,10 +1438,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="514350"/>
+    <ext cx="609600" cy="904875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="51" name="Image 51" descr="Picture"/>
@@ -1463,10 +1463,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="514350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="52" name="Image 52" descr="Picture"/>
@@ -1488,7 +1488,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1513,7 +1513,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1538,7 +1538,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1563,10 +1563,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="904875"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>
@@ -1588,10 +1588,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="904875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>
@@ -1613,7 +1613,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1638,7 +1638,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1663,7 +1663,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1688,7 +1688,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1713,7 +1713,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1738,7 +1738,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1763,10 +1763,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="409575"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="64" name="Image 64" descr="Picture"/>
@@ -1788,10 +1788,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="409575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="65" name="Image 65" descr="Picture"/>
@@ -1813,7 +1813,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1838,7 +1838,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1863,7 +1863,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1888,7 +1888,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1913,7 +1913,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1938,7 +1938,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1963,7 +1963,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -1988,7 +1988,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2013,7 +2013,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2038,7 +2038,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2063,7 +2063,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2088,7 +2088,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2113,7 +2113,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2138,7 +2138,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2163,7 +2163,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2188,7 +2188,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2213,7 +2213,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2238,7 +2238,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2263,7 +2263,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2288,7 +2288,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2313,7 +2313,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2338,7 +2338,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2363,7 +2363,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2388,7 +2388,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2413,7 +2413,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2438,7 +2438,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2463,7 +2463,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2488,7 +2488,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2513,7 +2513,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2538,7 +2538,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>119</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2563,7 +2563,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2588,7 +2588,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2613,7 +2613,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>122</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2638,7 +2638,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>123</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2663,7 +2663,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>124</row>
+      <row>123</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2688,7 +2688,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>125</row>
+      <row>124</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2713,7 +2713,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>126</row>
+      <row>125</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2738,7 +2738,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>126</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2763,7 +2763,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>128</row>
+      <row>127</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2788,7 +2788,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>129</row>
+      <row>128</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2813,7 +2813,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>129</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2838,7 +2838,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>131</row>
+      <row>130</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2863,10 +2863,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>132</row>
+      <row>131</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="762000"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="108" name="Image 108" descr="Picture"/>
@@ -2888,10 +2888,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="762000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="109" name="Image 109" descr="Picture"/>
@@ -2913,7 +2913,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>133</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -2938,10 +2938,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>135</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="762000"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="111" name="Image 111" descr="Picture"/>
@@ -2963,10 +2963,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>136</row>
+      <row>135</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="762000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="112" name="Image 112" descr="Picture"/>
@@ -2988,10 +2988,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>136</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="733425"/>
+    <ext cx="609600" cy="914400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="113" name="Image 113" descr="Picture"/>
@@ -3013,10 +3013,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>138</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="914400"/>
+    <ext cx="609600" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="114" name="Image 114" descr="Picture"/>
@@ -3038,7 +3038,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>139</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3063,7 +3063,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>140</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3088,7 +3088,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>141</row>
+      <row>140</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3113,7 +3113,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>142</row>
+      <row>141</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3138,7 +3138,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>143</row>
+      <row>142</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3163,7 +3163,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>144</row>
+      <row>143</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3188,7 +3188,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>145</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3213,7 +3213,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>146</row>
+      <row>145</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3238,7 +3238,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>147</row>
+      <row>146</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3263,7 +3263,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>148</row>
+      <row>147</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3288,7 +3288,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>149</row>
+      <row>148</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3313,7 +3313,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>150</row>
+      <row>149</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3338,7 +3338,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>151</row>
+      <row>150</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3363,7 +3363,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>152</row>
+      <row>151</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3388,7 +3388,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>153</row>
+      <row>152</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3413,7 +3413,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>154</row>
+      <row>153</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3438,7 +3438,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>155</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3463,7 +3463,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>156</row>
+      <row>155</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3488,7 +3488,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>157</row>
+      <row>156</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3513,7 +3513,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>158</row>
+      <row>157</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3538,7 +3538,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>159</row>
+      <row>158</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3563,7 +3563,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>160</row>
+      <row>159</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3588,7 +3588,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>161</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3613,7 +3613,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>162</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3638,7 +3638,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>163</row>
+      <row>162</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3663,7 +3663,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>163</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3688,7 +3688,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>165</row>
+      <row>164</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3713,7 +3713,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>166</row>
+      <row>165</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3738,7 +3738,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>167</row>
+      <row>166</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3763,7 +3763,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>168</row>
+      <row>167</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3788,7 +3788,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>169</row>
+      <row>168</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3813,7 +3813,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>170</row>
+      <row>169</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3838,7 +3838,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>171</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3863,7 +3863,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>172</row>
+      <row>171</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3888,7 +3888,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>172</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3913,7 +3913,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>174</row>
+      <row>173</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3938,7 +3938,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>175</row>
+      <row>174</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3963,7 +3963,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>176</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -3988,7 +3988,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>177</row>
+      <row>176</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4013,7 +4013,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>178</row>
+      <row>177</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4038,7 +4038,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>179</row>
+      <row>178</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4063,7 +4063,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>180</row>
+      <row>179</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4088,7 +4088,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>181</row>
+      <row>180</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4113,7 +4113,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>182</row>
+      <row>181</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4138,7 +4138,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>183</row>
+      <row>182</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -4163,7 +4163,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>184</row>
+      <row>183</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -4188,7 +4188,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>185</row>
+      <row>184</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="914400"/>
@@ -4501,7 +4501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM186"/>
+  <dimension ref="A1:BM185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix1</t>
+          <t>canyon_mix2</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix2</t>
+          <t>canyon_mix3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix3</t>
+          <t>canyon_mix4</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix4</t>
+          <t>canyon_mix5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix5</t>
+          <t>canyon_mix6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix6</t>
+          <t>canyon_mix7</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix7</t>
+          <t>canyon_mix8</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix8</t>
+          <t>canyon_mix9</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix9</t>
+          <t>canyon_mix10</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix10</t>
+          <t>canyon_mix11</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix11</t>
+          <t>canyon_mix12</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -12515,7 +12515,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="74.88" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>041</t>
@@ -12523,18 +12523,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>canyon_mix12</t>
+          <t>canyon_colossus</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>resources/enemy/mon_canyon_colossus_dark.webp</t>
+        </is>
+      </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>禍魘大軍</t>
+          <t>崩岩巨像</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -12546,31 +12550,31 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="4" t="inlineStr"/>
       <c r="R45" s="4" t="inlineStr"/>
@@ -12578,9 +12582,11 @@
       <c r="T45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="4" t="inlineStr"/>
+      <c r="U45" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V45" s="4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="W45" s="4" t="n">
         <v>0</v>
@@ -12592,14 +12598,14 @@
         <v>0</v>
       </c>
       <c r="Z45" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB45" s="4" t="inlineStr">
         <is>
-          <t>[9, 9, 9, 9, 16]</t>
+          <t>[9, 9, 9, 16, 16]</t>
         </is>
       </c>
       <c r="AC45" s="4" t="n">
@@ -12610,10 +12616,10 @@
       </c>
       <c r="AE45" s="4" t="inlineStr"/>
       <c r="AF45" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG45" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH45" s="4" t="n">
         <v>1</v>
@@ -12646,12 +12652,12 @@
       <c r="AR45" s="4" t="inlineStr"/>
       <c r="AS45" s="4" t="inlineStr">
         <is>
+          <t>blunt</t>
+        </is>
+      </c>
+      <c r="AT45" s="4" t="inlineStr">
+        <is>
           <t>blood</t>
-        </is>
-      </c>
-      <c r="AT45" s="4" t="inlineStr">
-        <is>
-          <t>slash</t>
         </is>
       </c>
       <c r="AU45" s="4" t="inlineStr">
@@ -12662,8 +12668,16 @@
       <c r="AV45" s="4" t="inlineStr"/>
       <c r="AW45" s="4" t="inlineStr"/>
       <c r="AX45" s="4" t="inlineStr"/>
-      <c r="AY45" s="4" t="inlineStr"/>
-      <c r="AZ45" s="4" t="inlineStr"/>
+      <c r="AY45" s="4" t="inlineStr">
+        <is>
+          <t>contain</t>
+        </is>
+      </c>
+      <c r="AZ45" s="4" t="inlineStr">
+        <is>
+          <t>center bottom</t>
+        </is>
+      </c>
       <c r="BA45" s="4" t="inlineStr"/>
       <c r="BB45" s="4" t="inlineStr"/>
       <c r="BC45" s="4" t="inlineStr"/>
@@ -33211,7 +33225,7 @@
       <c r="C165" s="4" t="inlineStr"/>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_colossus_dark.webp</t>
+          <t>resources/enemy/mon_canyon_crawler.webp</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr"/>
@@ -33298,7 +33312,7 @@
       <c r="C166" s="4" t="inlineStr"/>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_crawler.webp</t>
+          <t>resources/enemy/mon_canyon_crawler_dark.webp</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr"/>
@@ -33385,7 +33399,7 @@
       <c r="C167" s="4" t="inlineStr"/>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_crawler_dark.webp</t>
+          <t>resources/enemy/mon_canyon_hanged.webp</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr"/>
@@ -33472,7 +33486,7 @@
       <c r="C168" s="4" t="inlineStr"/>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_hanged.webp</t>
+          <t>resources/enemy/mon_canyon_hanged_dark.webp</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr"/>
@@ -33559,7 +33573,7 @@
       <c r="C169" s="4" t="inlineStr"/>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_hanged_dark.webp</t>
+          <t>resources/enemy/mon_canyon_houndbeast.webp</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr"/>
@@ -33646,7 +33660,7 @@
       <c r="C170" s="4" t="inlineStr"/>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_houndbeast.webp</t>
+          <t>resources/enemy/mon_canyon_ironpenitent.webp</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr"/>
@@ -33733,7 +33747,7 @@
       <c r="C171" s="4" t="inlineStr"/>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_ironpenitent.webp</t>
+          <t>resources/enemy/mon_canyon_ironpenitent_dark.webp</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr"/>
@@ -33820,7 +33834,7 @@
       <c r="C172" s="4" t="inlineStr"/>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_ironpenitent_dark.webp</t>
+          <t>resources/enemy/mon_canyon_lanternimp.webp</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr"/>
@@ -33907,7 +33921,7 @@
       <c r="C173" s="4" t="inlineStr"/>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_lanternimp.webp</t>
+          <t>resources/enemy/mon_canyon_lanternimp_dark.webp</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr"/>
@@ -33994,7 +34008,7 @@
       <c r="C174" s="4" t="inlineStr"/>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_lanternimp_dark.webp</t>
+          <t>resources/enemy/mon_canyon_pilgrimmass.webp</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr"/>
@@ -34081,7 +34095,7 @@
       <c r="C175" s="4" t="inlineStr"/>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_pilgrimmass.webp</t>
+          <t>resources/enemy/mon_canyon_pilgrimmass_dark.webp</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr"/>
@@ -34168,7 +34182,7 @@
       <c r="C176" s="4" t="inlineStr"/>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_pilgrimmass_dark.webp</t>
+          <t>resources/enemy/mon_canyon_ribcage.webp</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr"/>
@@ -34255,7 +34269,7 @@
       <c r="C177" s="4" t="inlineStr"/>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_ribcage.webp</t>
+          <t>resources/enemy/mon_canyon_ribcage_dark.webp</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr"/>
@@ -34342,7 +34356,7 @@
       <c r="C178" s="4" t="inlineStr"/>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_ribcage_dark.webp</t>
+          <t>resources/enemy/mon_canyon_saintvulture.webp</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr"/>
@@ -34429,7 +34443,7 @@
       <c r="C179" s="4" t="inlineStr"/>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_saintvulture.webp</t>
+          <t>resources/enemy/mon_canyon_saintvulture_dark.webp</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr"/>
@@ -34516,7 +34530,7 @@
       <c r="C180" s="4" t="inlineStr"/>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_saintvulture_dark.webp</t>
+          <t>resources/enemy/mon_canyon_stilt.webp</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr"/>
@@ -34603,7 +34617,7 @@
       <c r="C181" s="4" t="inlineStr"/>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_stilt.webp</t>
+          <t>resources/enemy/mon_canyon_stilt_dark.webp</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr"/>
@@ -34690,7 +34704,7 @@
       <c r="C182" s="4" t="inlineStr"/>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_canyon_stilt_dark.webp</t>
+          <t>resources/enemy/mon_dragon_throne_dormant.webp</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr"/>
@@ -34767,7 +34781,7 @@
       <c r="BL182" s="4" t="inlineStr"/>
       <c r="BM182" s="4" t="inlineStr"/>
     </row>
-    <row r="183" ht="74.88" customHeight="1">
+    <row r="183" ht="49.92" customHeight="1">
       <c r="A183" s="4" t="inlineStr">
         <is>
           <t>179</t>
@@ -34777,7 +34791,7 @@
       <c r="C183" s="4" t="inlineStr"/>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_dragon_throne_dormant.webp</t>
+          <t>resources/enemy/mon_gravekeeper_offset_body.webp</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr"/>
@@ -34864,7 +34878,7 @@
       <c r="C184" s="4" t="inlineStr"/>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_gravekeeper_offset_body.webp</t>
+          <t>resources/enemy/mon_gravekeeper_offset_soul.webp</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr"/>
@@ -34941,7 +34955,7 @@
       <c r="BL184" s="4" t="inlineStr"/>
       <c r="BM184" s="4" t="inlineStr"/>
     </row>
-    <row r="185" ht="49.92" customHeight="1">
+    <row r="185" ht="74.88" customHeight="1">
       <c r="A185" s="4" t="inlineStr">
         <is>
           <t>181</t>
@@ -34951,7 +34965,7 @@
       <c r="C185" s="4" t="inlineStr"/>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>resources/enemy/mon_gravekeeper_offset_soul.webp</t>
+          <t>resources/enemy/mon_gravekeeper_seal_down.webp</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr"/>
@@ -35028,93 +35042,6 @@
       <c r="BL185" s="4" t="inlineStr"/>
       <c r="BM185" s="4" t="inlineStr"/>
     </row>
-    <row r="186" ht="74.88" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr"/>
-      <c r="C186" s="4" t="inlineStr"/>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>resources/enemy/mon_gravekeeper_seal_down.webp</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr"/>
-      <c r="F186" s="4" t="inlineStr"/>
-      <c r="G186" s="4" t="inlineStr"/>
-      <c r="H186" s="4" t="inlineStr"/>
-      <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="4" t="inlineStr"/>
-      <c r="K186" s="4" t="inlineStr"/>
-      <c r="L186" s="4" t="inlineStr"/>
-      <c r="M186" s="4" t="inlineStr"/>
-      <c r="N186" s="4" t="inlineStr"/>
-      <c r="O186" s="4" t="inlineStr"/>
-      <c r="P186" s="4" t="inlineStr"/>
-      <c r="Q186" s="4" t="inlineStr"/>
-      <c r="R186" s="4" t="inlineStr"/>
-      <c r="S186" s="4" t="inlineStr"/>
-      <c r="T186" s="4" t="inlineStr"/>
-      <c r="U186" s="4" t="inlineStr"/>
-      <c r="V186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB186" s="4" t="inlineStr"/>
-      <c r="AC186" s="4" t="inlineStr"/>
-      <c r="AD186" s="4" t="inlineStr"/>
-      <c r="AE186" s="4" t="inlineStr"/>
-      <c r="AF186" s="4" t="inlineStr"/>
-      <c r="AG186" s="4" t="inlineStr"/>
-      <c r="AH186" s="4" t="inlineStr"/>
-      <c r="AI186" s="4" t="inlineStr"/>
-      <c r="AJ186" s="4" t="inlineStr"/>
-      <c r="AK186" s="4" t="inlineStr"/>
-      <c r="AL186" s="4" t="inlineStr"/>
-      <c r="AM186" s="4" t="inlineStr"/>
-      <c r="AN186" s="4" t="inlineStr"/>
-      <c r="AO186" s="4" t="inlineStr"/>
-      <c r="AP186" s="4" t="inlineStr"/>
-      <c r="AQ186" s="4" t="inlineStr"/>
-      <c r="AR186" s="4" t="inlineStr"/>
-      <c r="AS186" s="4" t="inlineStr"/>
-      <c r="AT186" s="4" t="inlineStr"/>
-      <c r="AU186" s="4" t="inlineStr"/>
-      <c r="AV186" s="4" t="inlineStr"/>
-      <c r="AW186" s="4" t="inlineStr"/>
-      <c r="AX186" s="4" t="inlineStr"/>
-      <c r="AY186" s="4" t="inlineStr"/>
-      <c r="AZ186" s="4" t="inlineStr"/>
-      <c r="BA186" s="4" t="inlineStr"/>
-      <c r="BB186" s="4" t="inlineStr"/>
-      <c r="BC186" s="4" t="inlineStr"/>
-      <c r="BD186" s="4" t="inlineStr"/>
-      <c r="BE186" s="4" t="inlineStr"/>
-      <c r="BF186" s="4" t="inlineStr"/>
-      <c r="BG186" s="4" t="inlineStr"/>
-      <c r="BH186" s="4" t="inlineStr"/>
-      <c r="BI186" s="4" t="inlineStr"/>
-      <c r="BJ186" s="4" t="inlineStr"/>
-      <c r="BK186" s="4" t="inlineStr"/>
-      <c r="BL186" s="4" t="inlineStr"/>
-      <c r="BM186" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B1:E1"/>
@@ -35130,31 +35057,31 @@
     <mergeCell ref="A1:A3"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="R4:R186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="R4:R185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$A$2:$A$22</formula1>
     </dataValidation>
-    <dataValidation sqref="BA4:BA186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BA4:BA185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BD4:BD186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BD4:BD185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BG4:BG186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BG4:BG185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="BJ4:BJ186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="BJ4:BJ185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$B$2:$B$49</formula1>
     </dataValidation>
-    <dataValidation sqref="AS4:AS186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AS4:AS185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AT4:AT186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AT4:AT185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AU4:AU186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AU4:AU185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="AV4:AV186" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AV4:AV185" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" type="list">
       <formula1>'__lists__'!$C$2:$C$20</formula1>
     </dataValidation>
   </dataValidations>
@@ -37510,7 +37437,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>b5df592826ea5d22cf698994e375f7073264a7a3c33cbc0f1c23d4489bfb9dc0</t>
+          <t>7a21432118938a31ec6c9d96c83dfa297d0d047f6867587e5c88a1d2fbbdd844</t>
         </is>
       </c>
     </row>

--- a/enemies.xlsx
+++ b/enemies.xlsx
@@ -12675,7 +12675,7 @@
       </c>
       <c r="AZ45" s="4" t="inlineStr">
         <is>
-          <t>center bottom</t>
+          <t>50% 100%</t>
         </is>
       </c>
       <c r="BA45" s="4" t="inlineStr"/>
@@ -37437,7 +37437,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>7a21432118938a31ec6c9d96c83dfa297d0d047f6867587e5c88a1d2fbbdd844</t>
+          <t>0770cd5083f8e0bcf3a7d088271b7098da9fc50d69c8683b4e97231306f99ccc</t>
         </is>
       </c>
     </row>
